--- a/jogos_2025-10-15.xlsx
+++ b/jogos_2025-10-15.xlsx
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Leopards</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Bandari</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L8" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Leopards</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bandari</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1568,7 +1568,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L9" t="n">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,13 +2475,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.75</v>
+        <v>2.14</v>
       </c>
       <c r="M16" t="n">
-        <v>3</v>
+        <v>3.14</v>
       </c>
       <c r="N16" t="n">
-        <v>2.75</v>
+        <v>2.99</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2508,7 +2508,7 @@
         <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="X16" t="n">
         <v>2.45</v>
@@ -2517,7 +2517,7 @@
         <v>2.45</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AA16" t="n">
         <v>0</v>
@@ -2604,13 +2604,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.2</v>
+        <v>2.11</v>
       </c>
       <c r="M17" t="n">
-        <v>3.15</v>
+        <v>2.87</v>
       </c>
       <c r="N17" t="n">
-        <v>3.55</v>
+        <v>3.36</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,13 +2733,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.3</v>
+        <v>2.47</v>
       </c>
       <c r="M18" t="n">
-        <v>3.25</v>
+        <v>2.93</v>
       </c>
       <c r="N18" t="n">
-        <v>3.15</v>
+        <v>2.68</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2766,7 +2766,7 @@
         <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="X18" t="n">
         <v>2.45</v>
@@ -2775,7 +2775,7 @@
         <v>2.45</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AA18" t="n">
         <v>0</v>

--- a/jogos_2025-10-15.xlsx
+++ b/jogos_2025-10-15.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK19"/>
+  <dimension ref="A1:AK20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1015,7 +1015,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sur</t>
+          <t>Ibri</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1135,7 +1135,7 @@
         <v>0</v>
       </c>
       <c r="AK5" s="3" t="n">
-        <v>45945.42361111111</v>
+        <v>45945.41666666666</v>
       </c>
     </row>
     <row r="6">
@@ -1144,27 +1144,27 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Sur</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1264,7 +1264,7 @@
         <v>0</v>
       </c>
       <c r="AK6" s="3" t="n">
-        <v>45945.45833333334</v>
+        <v>45945.42361111111</v>
       </c>
     </row>
     <row r="7">
@@ -1273,27 +1273,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Dhofar</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Smail</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1393,7 +1393,7 @@
         <v>0</v>
       </c>
       <c r="AK7" s="3" t="n">
-        <v>45945.47569444445</v>
+        <v>45945.45833333334</v>
       </c>
     </row>
     <row r="8">
@@ -1402,12 +1402,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Leopards</t>
+          <t>Dhofar</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bandari</t>
+          <t>Smail</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1522,7 +1522,7 @@
         <v>0</v>
       </c>
       <c r="AK8" s="3" t="n">
-        <v>45945.5</v>
+        <v>45945.47569444445</v>
       </c>
     </row>
     <row r="9">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Leopards</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Bandari</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1568,7 +1568,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L9" t="n">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al-Rustaq</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Saham</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1697,7 +1697,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L10" t="n">
@@ -1780,7 +1780,7 @@
         <v>0</v>
       </c>
       <c r="AK10" s="3" t="n">
-        <v>45945.52777777778</v>
+        <v>45945.5</v>
       </c>
     </row>
     <row r="11">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Al-Rustaq</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="AK11" s="3" t="n">
-        <v>45945.54166666666</v>
+        <v>45945.52777777778</v>
       </c>
     </row>
     <row r="12">
@@ -1918,27 +1918,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,13 +1959,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.36</v>
+        <v>7.5</v>
       </c>
       <c r="M12" t="n">
-        <v>4.1</v>
+        <v>4.15</v>
       </c>
       <c r="N12" t="n">
-        <v>7.2</v>
+        <v>1.42</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1998,10 +1998,10 @@
         <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="AA12" t="n">
         <v>0</v>
@@ -2038,7 +2038,7 @@
         <v>0</v>
       </c>
       <c r="AK12" s="3" t="n">
-        <v>45945.79166666666</v>
+        <v>45945.54166666666</v>
       </c>
     </row>
     <row r="13">
@@ -2047,7 +2047,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>3.65</v>
+        <v>1.36</v>
       </c>
       <c r="M13" t="n">
-        <v>2.95</v>
+        <v>4.1</v>
       </c>
       <c r="N13" t="n">
-        <v>1.97</v>
+        <v>7.2</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2127,10 +2127,10 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.25</v>
+        <v>1.78</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.65</v>
+        <v>1.92</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -2167,7 +2167,7 @@
         <v>0</v>
       </c>
       <c r="AK13" s="3" t="n">
-        <v>45945.8125</v>
+        <v>45945.79166666666</v>
       </c>
     </row>
     <row r="14">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,13 +2217,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.24</v>
+        <v>3.65</v>
       </c>
       <c r="M14" t="n">
-        <v>2.84</v>
+        <v>2.95</v>
       </c>
       <c r="N14" t="n">
-        <v>3.12</v>
+        <v>1.97</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2250,16 +2250,16 @@
         <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>
@@ -2296,7 +2296,7 @@
         <v>0</v>
       </c>
       <c r="AK14" s="3" t="n">
-        <v>45945.83333333334</v>
+        <v>45945.8125</v>
       </c>
     </row>
     <row r="15">
@@ -2434,7 +2434,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,13 +2475,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.14</v>
+        <v>2.24</v>
       </c>
       <c r="M16" t="n">
-        <v>3.14</v>
+        <v>2.84</v>
       </c>
       <c r="N16" t="n">
-        <v>2.99</v>
+        <v>3.12</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2508,16 +2508,16 @@
         <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="X16" t="n">
         <v>2.45</v>
       </c>
       <c r="Y16" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AA16" t="n">
         <v>0</v>
@@ -2554,7 +2554,7 @@
         <v>0</v>
       </c>
       <c r="AK16" s="3" t="n">
-        <v>45945.89583333334</v>
+        <v>45945.83333333334</v>
       </c>
     </row>
     <row r="17">
@@ -2821,126 +2821,255 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Fortaleza</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Vasco da Gama</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L19" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="M19" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="N19" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="X19" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK19" s="3" t="n">
+        <v>45945.89583333334</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>45945</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
           <t>23:00</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>USA USL Championship</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>Orange County SC</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>San Antonio</t>
         </is>
       </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>suspended</t>
-        </is>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
-        <v>0</v>
-      </c>
-      <c r="T19" t="n">
-        <v>0</v>
-      </c>
-      <c r="U19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" t="n">
-        <v>0</v>
-      </c>
-      <c r="W19" t="n">
-        <v>0</v>
-      </c>
-      <c r="X19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK19" s="3" t="n">
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0</v>
+      </c>
+      <c r="X20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK20" s="3" t="n">
         <v>45945.95833333334</v>
       </c>
     </row>

--- a/jogos_2025-10-15.xlsx
+++ b/jogos_2025-10-15.xlsx
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,13 +2346,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.99</v>
+        <v>2.24</v>
       </c>
       <c r="M15" t="n">
-        <v>3.11</v>
+        <v>2.84</v>
       </c>
       <c r="N15" t="n">
-        <v>3.39</v>
+        <v>3.12</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2379,16 +2379,16 @@
         <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Y15" t="n">
-        <v>2.12</v>
+        <v>2.5</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.72</v>
+        <v>1.53</v>
       </c>
       <c r="AA15" t="n">
         <v>0</v>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,13 +2475,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.24</v>
+        <v>1.99</v>
       </c>
       <c r="M16" t="n">
-        <v>2.84</v>
+        <v>3.11</v>
       </c>
       <c r="N16" t="n">
-        <v>3.12</v>
+        <v>3.39</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2508,16 +2508,16 @@
         <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>2.5</v>
+        <v>2.12</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.53</v>
+        <v>1.72</v>
       </c>
       <c r="AA16" t="n">
         <v>0</v>
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,13 +2604,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.11</v>
+        <v>2.47</v>
       </c>
       <c r="M17" t="n">
-        <v>2.87</v>
+        <v>2.93</v>
       </c>
       <c r="N17" t="n">
-        <v>3.36</v>
+        <v>2.68</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2637,16 +2637,16 @@
         <v>0</v>
       </c>
       <c r="W17" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X17" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Z17" t="n">
         <v>1.55</v>
-      </c>
-      <c r="X17" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>1.47</v>
       </c>
       <c r="AA17" t="n">
         <v>0</v>
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,13 +2733,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.47</v>
+        <v>2.11</v>
       </c>
       <c r="M18" t="n">
-        <v>2.93</v>
+        <v>2.87</v>
       </c>
       <c r="N18" t="n">
-        <v>2.68</v>
+        <v>3.36</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2766,16 +2766,16 @@
         <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="X18" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.45</v>
+        <v>2.6</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.55</v>
+        <v>1.47</v>
       </c>
       <c r="AA18" t="n">
         <v>0</v>

--- a/jogos_2025-10-15.xlsx
+++ b/jogos_2025-10-15.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK20"/>
+  <dimension ref="A1:AK19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1273,27 +1273,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Dhofar</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Smail</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1393,7 +1393,7 @@
         <v>0</v>
       </c>
       <c r="AK7" s="3" t="n">
-        <v>45945.45833333334</v>
+        <v>45945.47569444445</v>
       </c>
     </row>
     <row r="8">
@@ -1402,12 +1402,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Dhofar</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Smail</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L8" t="n">
@@ -1522,7 +1522,7 @@
         <v>0</v>
       </c>
       <c r="AK8" s="3" t="n">
-        <v>45945.47569444445</v>
+        <v>45945.5</v>
       </c>
     </row>
     <row r="9">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Al-Rustaq</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1697,7 +1697,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L10" t="n">
@@ -1780,7 +1780,7 @@
         <v>0</v>
       </c>
       <c r="AK10" s="3" t="n">
-        <v>45945.5</v>
+        <v>45945.52777777778</v>
       </c>
     </row>
     <row r="11">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al-Rustaq</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Saham</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,13 +1830,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1869,10 +1869,10 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="AK11" s="3" t="n">
-        <v>45945.52777777778</v>
+        <v>45945.54166666666</v>
       </c>
     </row>
     <row r="12">
@@ -1918,27 +1918,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,13 +1959,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>7.5</v>
+        <v>1.36</v>
       </c>
       <c r="M12" t="n">
-        <v>4.15</v>
+        <v>4.1</v>
       </c>
       <c r="N12" t="n">
-        <v>1.42</v>
+        <v>7.2</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1998,10 +1998,10 @@
         <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="AA12" t="n">
         <v>0</v>
@@ -2038,7 +2038,7 @@
         <v>0</v>
       </c>
       <c r="AK12" s="3" t="n">
-        <v>45945.54166666666</v>
+        <v>45945.79166666666</v>
       </c>
     </row>
     <row r="13">
@@ -2047,7 +2047,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.36</v>
+        <v>3.65</v>
       </c>
       <c r="M13" t="n">
-        <v>4.1</v>
+        <v>2.95</v>
       </c>
       <c r="N13" t="n">
-        <v>7.2</v>
+        <v>1.97</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2127,10 +2127,10 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.78</v>
+        <v>2.25</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.92</v>
+        <v>1.65</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -2167,7 +2167,7 @@
         <v>0</v>
       </c>
       <c r="AK13" s="3" t="n">
-        <v>45945.79166666666</v>
+        <v>45945.8125</v>
       </c>
     </row>
     <row r="14">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,13 +2217,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.65</v>
+        <v>1.99</v>
       </c>
       <c r="M14" t="n">
-        <v>2.95</v>
+        <v>3.11</v>
       </c>
       <c r="N14" t="n">
-        <v>1.97</v>
+        <v>3.39</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2256,10 +2256,10 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>2.25</v>
+        <v>2.12</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>
@@ -2296,7 +2296,7 @@
         <v>0</v>
       </c>
       <c r="AK14" s="3" t="n">
-        <v>45945.8125</v>
+        <v>45945.83333333334</v>
       </c>
     </row>
     <row r="15">
@@ -2434,7 +2434,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,13 +2475,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.99</v>
+        <v>2.11</v>
       </c>
       <c r="M16" t="n">
-        <v>3.11</v>
+        <v>2.87</v>
       </c>
       <c r="N16" t="n">
-        <v>3.39</v>
+        <v>3.36</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2508,16 +2508,16 @@
         <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Y16" t="n">
-        <v>2.12</v>
+        <v>2.6</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.72</v>
+        <v>1.47</v>
       </c>
       <c r="AA16" t="n">
         <v>0</v>
@@ -2554,7 +2554,7 @@
         <v>0</v>
       </c>
       <c r="AK16" s="3" t="n">
-        <v>45945.83333333334</v>
+        <v>45945.89583333334</v>
       </c>
     </row>
     <row r="17">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,13 +2733,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.11</v>
+        <v>2.14</v>
       </c>
       <c r="M18" t="n">
-        <v>2.87</v>
+        <v>3.14</v>
       </c>
       <c r="N18" t="n">
-        <v>3.36</v>
+        <v>2.99</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2769,13 +2769,13 @@
         <v>1.55</v>
       </c>
       <c r="X18" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AA18" t="n">
         <v>0</v>
@@ -2821,12 +2821,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,13 +2862,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2895,16 +2895,16 @@
         <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
         <v>0</v>
@@ -2941,135 +2941,6 @@
         <v>0</v>
       </c>
       <c r="AK19" s="3" t="n">
-        <v>45945.89583333334</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="n">
-        <v>45945</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>USA USL Championship</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Orange County SC</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>San Antonio</t>
-        </is>
-      </c>
-      <c r="G20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="n">
-        <v>0</v>
-      </c>
-      <c r="T20" t="n">
-        <v>0</v>
-      </c>
-      <c r="U20" t="n">
-        <v>0</v>
-      </c>
-      <c r="V20" t="n">
-        <v>0</v>
-      </c>
-      <c r="W20" t="n">
-        <v>0</v>
-      </c>
-      <c r="X20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK20" s="3" t="n">
         <v>45945.95833333334</v>
       </c>
     </row>

--- a/jogos_2025-10-15.xlsx
+++ b/jogos_2025-10-15.xlsx
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Leopards</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Bandari</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L8" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Leopards</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bandari</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1568,7 +1568,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L9" t="n">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,13 +2475,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.11</v>
+        <v>2.47</v>
       </c>
       <c r="M16" t="n">
-        <v>2.87</v>
+        <v>2.93</v>
       </c>
       <c r="N16" t="n">
-        <v>3.36</v>
+        <v>2.68</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2508,16 +2508,16 @@
         <v>0</v>
       </c>
       <c r="W16" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X16" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Z16" t="n">
         <v>1.55</v>
-      </c>
-      <c r="X16" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>1.47</v>
       </c>
       <c r="AA16" t="n">
         <v>0</v>
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,13 +2604,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.47</v>
+        <v>2.14</v>
       </c>
       <c r="M17" t="n">
-        <v>2.93</v>
+        <v>3.14</v>
       </c>
       <c r="N17" t="n">
-        <v>2.68</v>
+        <v>2.99</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2637,7 +2637,7 @@
         <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="X17" t="n">
         <v>2.45</v>
@@ -2646,7 +2646,7 @@
         <v>2.45</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AA17" t="n">
         <v>0</v>
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,13 +2733,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.14</v>
+        <v>2.11</v>
       </c>
       <c r="M18" t="n">
-        <v>3.14</v>
+        <v>2.87</v>
       </c>
       <c r="N18" t="n">
-        <v>2.99</v>
+        <v>3.36</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2769,13 +2769,13 @@
         <v>1.55</v>
       </c>
       <c r="X18" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.45</v>
+        <v>2.6</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AA18" t="n">
         <v>0</v>
@@ -2862,13 +2862,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2901,10 +2901,10 @@
         <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA19" t="n">
         <v>0</v>

--- a/jogos_2025-10-15.xlsx
+++ b/jogos_2025-10-15.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK19"/>
+  <dimension ref="A1:AK18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Homeboyz</t>
+          <t>Murang'a SEAL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bidco United</t>
+          <t>Sofapaka</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Murang'a SEAL</t>
+          <t>Homeboyz</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sofapaka</t>
+          <t>Bidco United</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1531,12 +1531,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Al-Rustaq</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1568,7 +1568,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L9" t="n">
@@ -1651,7 +1651,7 @@
         <v>0</v>
       </c>
       <c r="AK9" s="3" t="n">
-        <v>45945.5</v>
+        <v>45945.52777777778</v>
       </c>
     </row>
     <row r="10">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al-Rustaq</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Saham</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,61 +1701,61 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>6.53</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1780,7 +1780,7 @@
         <v>0</v>
       </c>
       <c r="AK10" s="3" t="n">
-        <v>45945.52777777778</v>
+        <v>45945.54166666666</v>
       </c>
     </row>
     <row r="11">
@@ -1789,27 +1789,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>7.5</v>
+        <v>1.36</v>
       </c>
       <c r="M11" t="n">
-        <v>4.15</v>
+        <v>4.1</v>
       </c>
       <c r="N11" t="n">
-        <v>1.42</v>
+        <v>7.2</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="AK11" s="3" t="n">
-        <v>45945.54166666666</v>
+        <v>45945.79166666666</v>
       </c>
     </row>
     <row r="12">
@@ -1918,7 +1918,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,61 +1959,61 @@
         </is>
       </c>
       <c r="L12" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="M12" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="N12" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="O12" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W12" t="n">
         <v>1.36</v>
       </c>
-      <c r="M12" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="N12" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T12" t="n">
-        <v>0</v>
-      </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" t="n">
-        <v>0</v>
-      </c>
-      <c r="W12" t="n">
-        <v>0</v>
-      </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.78</v>
+        <v>2.25</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.92</v>
+        <v>1.65</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2038,7 +2038,7 @@
         <v>0</v>
       </c>
       <c r="AK12" s="3" t="n">
-        <v>45945.79166666666</v>
+        <v>45945.8125</v>
       </c>
     </row>
     <row r="13">
@@ -2047,7 +2047,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,61 +2088,61 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>3.65</v>
+        <v>1.99</v>
       </c>
       <c r="M13" t="n">
-        <v>2.95</v>
+        <v>3.11</v>
       </c>
       <c r="N13" t="n">
-        <v>1.97</v>
+        <v>3.39</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.25</v>
+        <v>2.12</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AI13" t="n">
         <v>0</v>
@@ -2167,7 +2167,7 @@
         <v>0</v>
       </c>
       <c r="AK13" s="3" t="n">
-        <v>45945.8125</v>
+        <v>45945.83333333334</v>
       </c>
     </row>
     <row r="14">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,61 +2217,61 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.99</v>
+        <v>2.24</v>
       </c>
       <c r="M14" t="n">
-        <v>3.11</v>
+        <v>2.84</v>
       </c>
       <c r="N14" t="n">
-        <v>3.39</v>
+        <v>3.12</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Y14" t="n">
-        <v>2.12</v>
+        <v>2.5</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.72</v>
+        <v>1.53</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2305,7 +2305,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,61 +2346,61 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.24</v>
+        <v>2.11</v>
       </c>
       <c r="M15" t="n">
-        <v>2.84</v>
+        <v>2.87</v>
       </c>
       <c r="N15" t="n">
-        <v>3.12</v>
+        <v>3.36</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="W15" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="X15" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="Y15" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.53</v>
+        <v>1.43</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2425,7 +2425,7 @@
         <v>0</v>
       </c>
       <c r="AK15" s="3" t="n">
-        <v>45945.83333333334</v>
+        <v>45945.89583333334</v>
       </c>
     </row>
     <row r="16">
@@ -2484,28 +2484,28 @@
         <v>2.68</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="W16" t="n">
         <v>1.5</v>
@@ -2520,16 +2520,16 @@
         <v>1.55</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2613,28 +2613,28 @@
         <v>2.99</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W17" t="n">
         <v>1.55</v>
@@ -2649,16 +2649,16 @@
         <v>1.5</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2692,12 +2692,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,13 +2733,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.11</v>
+        <v>2.4</v>
       </c>
       <c r="M18" t="n">
-        <v>2.87</v>
+        <v>3.6</v>
       </c>
       <c r="N18" t="n">
-        <v>3.36</v>
+        <v>2.55</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2766,16 +2766,16 @@
         <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.6</v>
+        <v>1.9</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.47</v>
+        <v>1.8</v>
       </c>
       <c r="AA18" t="n">
         <v>0</v>
@@ -2812,135 +2812,6 @@
         <v>0</v>
       </c>
       <c r="AK18" s="3" t="n">
-        <v>45945.89583333334</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="n">
-        <v>45945</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>USA USL Championship</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Orange County SC</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>San Antonio</t>
-        </is>
-      </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L19" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="M19" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="N19" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
-        <v>0</v>
-      </c>
-      <c r="T19" t="n">
-        <v>0</v>
-      </c>
-      <c r="U19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" t="n">
-        <v>0</v>
-      </c>
-      <c r="W19" t="n">
-        <v>0</v>
-      </c>
-      <c r="X19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK19" s="3" t="n">
         <v>45945.95833333334</v>
       </c>
     </row>

--- a/jogos_2025-10-15.xlsx
+++ b/jogos_2025-10-15.xlsx
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Murang'a SEAL</t>
+          <t>Homeboyz</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sofapaka</t>
+          <t>Bidco United</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Homeboyz</t>
+          <t>Murang'a SEAL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bidco United</t>
+          <t>Sofapaka</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,61 +2346,61 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.11</v>
+        <v>2.14</v>
       </c>
       <c r="M15" t="n">
-        <v>2.87</v>
+        <v>3.14</v>
       </c>
       <c r="N15" t="n">
-        <v>3.36</v>
+        <v>2.99</v>
       </c>
       <c r="O15" t="n">
-        <v>2.9</v>
+        <v>2.85</v>
       </c>
       <c r="P15" t="n">
-        <v>1.88</v>
+        <v>2.03</v>
       </c>
       <c r="Q15" t="n">
-        <v>4.4</v>
+        <v>3.82</v>
       </c>
       <c r="R15" t="n">
-        <v>1.56</v>
+        <v>1.41</v>
       </c>
       <c r="S15" t="n">
-        <v>2.34</v>
+        <v>2.69</v>
       </c>
       <c r="T15" t="n">
-        <v>3.58</v>
+        <v>2.94</v>
       </c>
       <c r="U15" t="n">
-        <v>1.23</v>
+        <v>1.35</v>
       </c>
       <c r="V15" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="W15" t="n">
         <v>1.55</v>
       </c>
       <c r="X15" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="Y15" t="n">
-        <v>2.48</v>
+        <v>2.45</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="AA15" t="n">
-        <v>4.9</v>
+        <v>3.44</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.11</v>
+        <v>1.23</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.13</v>
+        <v>1.79</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.64</v>
+        <v>1.92</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,61 +2475,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.47</v>
+        <v>2.11</v>
       </c>
       <c r="M16" t="n">
-        <v>2.93</v>
+        <v>2.87</v>
       </c>
       <c r="N16" t="n">
-        <v>2.68</v>
+        <v>3.36</v>
       </c>
       <c r="O16" t="n">
-        <v>3.25</v>
+        <v>2.9</v>
       </c>
       <c r="P16" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.4</v>
+        <v>4.4</v>
       </c>
       <c r="R16" t="n">
-        <v>1.44</v>
+        <v>1.56</v>
       </c>
       <c r="S16" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="T16" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="X16" t="n">
         <v>2.5</v>
       </c>
-      <c r="T16" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="X16" t="n">
-        <v>2.45</v>
-      </c>
       <c r="Y16" t="n">
-        <v>2.45</v>
+        <v>2.48</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.55</v>
+        <v>1.43</v>
       </c>
       <c r="AA16" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="AC16" t="n">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.75</v>
+        <v>1.64</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,40 +2604,40 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.14</v>
+        <v>2.47</v>
       </c>
       <c r="M17" t="n">
-        <v>3.14</v>
+        <v>2.93</v>
       </c>
       <c r="N17" t="n">
-        <v>2.99</v>
+        <v>2.68</v>
       </c>
       <c r="O17" t="n">
-        <v>2.85</v>
+        <v>3.25</v>
       </c>
       <c r="P17" t="n">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.82</v>
+        <v>3.4</v>
       </c>
       <c r="R17" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="S17" t="n">
-        <v>2.69</v>
+        <v>2.5</v>
       </c>
       <c r="T17" t="n">
-        <v>2.94</v>
+        <v>3.3</v>
       </c>
       <c r="U17" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="V17" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="W17" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="X17" t="n">
         <v>2.45</v>
@@ -2646,19 +2646,19 @@
         <v>2.45</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AA17" t="n">
-        <v>3.44</v>
+        <v>4.8</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.79</v>
+        <v>2</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.92</v>
+        <v>1.75</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.63</v>
+        <v>1.4</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>

--- a/jogos_2025-10-15.xlsx
+++ b/jogos_2025-10-15.xlsx
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Homeboyz</t>
+          <t>Murang'a SEAL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bidco United</t>
+          <t>Sofapaka</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Murang'a SEAL</t>
+          <t>Homeboyz</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sofapaka</t>
+          <t>Bidco United</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1830,34 +1830,34 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="M11" t="n">
-        <v>4.1</v>
+        <v>5.07</v>
       </c>
       <c r="N11" t="n">
-        <v>7.2</v>
+        <v>8.57</v>
       </c>
       <c r="O11" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="P11" t="n">
-        <v>2.33</v>
+        <v>2.34</v>
       </c>
       <c r="Q11" t="n">
         <v>7.1</v>
       </c>
       <c r="R11" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="S11" t="n">
-        <v>2.94</v>
+        <v>2.99</v>
       </c>
       <c r="T11" t="n">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="U11" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="V11" t="n">
         <v>1</v>
@@ -1869,16 +1869,16 @@
         <v>3.44</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.78</v>
+        <v>1.86</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.92</v>
+        <v>1.99</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.89</v>
+        <v>2.85</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AC11" t="n">
         <v>2.06</v>
@@ -1962,10 +1962,10 @@
         <v>3.65</v>
       </c>
       <c r="M12" t="n">
-        <v>2.95</v>
+        <v>3.2</v>
       </c>
       <c r="N12" t="n">
-        <v>1.97</v>
+        <v>2.02</v>
       </c>
       <c r="O12" t="n">
         <v>4.6</v>
@@ -1998,10 +1998,10 @@
         <v>2.72</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AA12" t="n">
         <v>3.95</v>
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.99</v>
+        <v>2.08</v>
       </c>
       <c r="M13" t="n">
-        <v>3.11</v>
+        <v>3.32</v>
       </c>
       <c r="N13" t="n">
-        <v>3.39</v>
+        <v>3.35</v>
       </c>
       <c r="O13" t="n">
         <v>2.63</v>
@@ -2127,10 +2127,10 @@
         <v>3</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.12</v>
+        <v>2.05</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AA13" t="n">
         <v>3.75</v>
@@ -2217,13 +2217,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.24</v>
+        <v>2.34</v>
       </c>
       <c r="M14" t="n">
-        <v>2.84</v>
+        <v>3.18</v>
       </c>
       <c r="N14" t="n">
-        <v>3.12</v>
+        <v>3.2</v>
       </c>
       <c r="O14" t="n">
         <v>3</v>
@@ -2250,13 +2250,13 @@
         <v>1.08</v>
       </c>
       <c r="W14" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="X14" t="n">
-        <v>2.45</v>
+        <v>2.63</v>
       </c>
       <c r="Y14" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="Z14" t="n">
         <v>1.53</v>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,61 +2346,61 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.14</v>
+        <v>2.21</v>
       </c>
       <c r="M15" t="n">
-        <v>3.14</v>
+        <v>3.05</v>
       </c>
       <c r="N15" t="n">
-        <v>2.99</v>
+        <v>3.35</v>
       </c>
       <c r="O15" t="n">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="P15" t="n">
-        <v>2.03</v>
+        <v>1.88</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.82</v>
+        <v>4.4</v>
       </c>
       <c r="R15" t="n">
-        <v>1.41</v>
+        <v>1.56</v>
       </c>
       <c r="S15" t="n">
-        <v>2.69</v>
+        <v>2.34</v>
       </c>
       <c r="T15" t="n">
-        <v>2.94</v>
+        <v>3.58</v>
       </c>
       <c r="U15" t="n">
-        <v>1.35</v>
+        <v>1.23</v>
       </c>
       <c r="V15" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="W15" t="n">
         <v>1.55</v>
       </c>
       <c r="X15" t="n">
-        <v>2.45</v>
+        <v>2.53</v>
       </c>
       <c r="Y15" t="n">
-        <v>2.45</v>
+        <v>2.48</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="AA15" t="n">
-        <v>3.44</v>
+        <v>4.9</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.23</v>
+        <v>1.11</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.79</v>
+        <v>2.13</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.92</v>
+        <v>1.64</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,61 +2475,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.11</v>
+        <v>2.88</v>
       </c>
       <c r="M16" t="n">
-        <v>2.87</v>
+        <v>3.06</v>
       </c>
       <c r="N16" t="n">
-        <v>3.36</v>
+        <v>2.64</v>
       </c>
       <c r="O16" t="n">
-        <v>2.9</v>
+        <v>3.25</v>
       </c>
       <c r="P16" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.4</v>
+        <v>3.4</v>
       </c>
       <c r="R16" t="n">
-        <v>1.56</v>
+        <v>1.44</v>
       </c>
       <c r="S16" t="n">
-        <v>2.34</v>
+        <v>2.5</v>
       </c>
       <c r="T16" t="n">
-        <v>3.58</v>
+        <v>3.3</v>
       </c>
       <c r="U16" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="V16" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="W16" t="n">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="X16" t="n">
         <v>2.5</v>
       </c>
       <c r="Y16" t="n">
-        <v>2.48</v>
+        <v>2.4</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="AA16" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.67</v>
+        <v>1.4</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,61 +2604,61 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.47</v>
+        <v>2.14</v>
       </c>
       <c r="M17" t="n">
-        <v>2.93</v>
+        <v>3.14</v>
       </c>
       <c r="N17" t="n">
-        <v>2.68</v>
+        <v>2.99</v>
       </c>
       <c r="O17" t="n">
-        <v>3.25</v>
+        <v>2.86</v>
       </c>
       <c r="P17" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.4</v>
+        <v>3.84</v>
       </c>
       <c r="R17" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="S17" t="n">
-        <v>2.5</v>
+        <v>2.65</v>
       </c>
       <c r="T17" t="n">
-        <v>3.3</v>
+        <v>2.94</v>
       </c>
       <c r="U17" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="V17" t="n">
-        <v>1.1</v>
+        <v>1.02</v>
       </c>
       <c r="W17" t="n">
-        <v>1.5</v>
+        <v>1.31</v>
       </c>
       <c r="X17" t="n">
-        <v>2.45</v>
+        <v>2.94</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.45</v>
+        <v>2.12</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.55</v>
+        <v>1.75</v>
       </c>
       <c r="AA17" t="n">
-        <v>4.8</v>
+        <v>3.54</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AC17" t="n">
-        <v>2</v>
+        <v>1.81</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.75</v>
+        <v>1.9</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.4</v>
+        <v>1.63</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>

--- a/jogos_2025-10-15.xlsx
+++ b/jogos_2025-10-15.xlsx
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Murang'a SEAL</t>
+          <t>Homeboyz</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sofapaka</t>
+          <t>Bidco United</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Homeboyz</t>
+          <t>Murang'a SEAL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bidco United</t>
+          <t>Sofapaka</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,61 +2346,61 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.21</v>
+        <v>2.14</v>
       </c>
       <c r="M15" t="n">
-        <v>3.05</v>
+        <v>3.14</v>
       </c>
       <c r="N15" t="n">
-        <v>3.35</v>
+        <v>2.99</v>
       </c>
       <c r="O15" t="n">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="P15" t="n">
-        <v>1.88</v>
+        <v>2.02</v>
       </c>
       <c r="Q15" t="n">
-        <v>4.4</v>
+        <v>3.84</v>
       </c>
       <c r="R15" t="n">
-        <v>1.56</v>
+        <v>1.42</v>
       </c>
       <c r="S15" t="n">
-        <v>2.34</v>
+        <v>2.65</v>
       </c>
       <c r="T15" t="n">
-        <v>3.58</v>
+        <v>2.94</v>
       </c>
       <c r="U15" t="n">
-        <v>1.23</v>
+        <v>1.35</v>
       </c>
       <c r="V15" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="W15" t="n">
-        <v>1.55</v>
+        <v>1.31</v>
       </c>
       <c r="X15" t="n">
-        <v>2.53</v>
+        <v>2.94</v>
       </c>
       <c r="Y15" t="n">
-        <v>2.48</v>
+        <v>2.12</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.43</v>
+        <v>1.75</v>
       </c>
       <c r="AA15" t="n">
-        <v>4.9</v>
+        <v>3.54</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.11</v>
+        <v>1.22</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.13</v>
+        <v>1.81</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.64</v>
+        <v>1.9</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,61 +2604,61 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.14</v>
+        <v>2.21</v>
       </c>
       <c r="M17" t="n">
-        <v>3.14</v>
+        <v>3.05</v>
       </c>
       <c r="N17" t="n">
-        <v>2.99</v>
+        <v>3.35</v>
       </c>
       <c r="O17" t="n">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="P17" t="n">
-        <v>2.02</v>
+        <v>1.88</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.84</v>
+        <v>4.4</v>
       </c>
       <c r="R17" t="n">
-        <v>1.42</v>
+        <v>1.56</v>
       </c>
       <c r="S17" t="n">
-        <v>2.65</v>
+        <v>2.34</v>
       </c>
       <c r="T17" t="n">
-        <v>2.94</v>
+        <v>3.58</v>
       </c>
       <c r="U17" t="n">
-        <v>1.35</v>
+        <v>1.23</v>
       </c>
       <c r="V17" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="W17" t="n">
-        <v>1.31</v>
+        <v>1.55</v>
       </c>
       <c r="X17" t="n">
-        <v>2.94</v>
+        <v>2.53</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.12</v>
+        <v>2.48</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.75</v>
+        <v>1.43</v>
       </c>
       <c r="AA17" t="n">
-        <v>3.54</v>
+        <v>4.9</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.22</v>
+        <v>1.11</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.81</v>
+        <v>2.13</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.9</v>
+        <v>1.64</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2736,58 +2736,58 @@
         <v>2.4</v>
       </c>
       <c r="M18" t="n">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="N18" t="n">
-        <v>2.55</v>
+        <v>2.7</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>

--- a/jogos_2025-10-15.xlsx
+++ b/jogos_2025-10-15.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK18"/>
+  <dimension ref="A1:AK19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -628,7 +628,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Shabana</t>
+          <t>Homeboyz</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Posta Rangers</t>
+          <t>Bidco United</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -748,7 +748,7 @@
         <v>0</v>
       </c>
       <c r="AK2" s="3" t="n">
-        <v>45945.33333333334</v>
+        <v>45945.375</v>
       </c>
     </row>
     <row r="3">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Homeboyz</t>
+          <t>Murang'a SEAL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bidco United</t>
+          <t>Sofapaka</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -886,12 +886,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Murang'a SEAL</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sofapaka</t>
+          <t>Ibri</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1006,7 +1006,7 @@
         <v>0</v>
       </c>
       <c r="AK4" s="3" t="n">
-        <v>45945.375</v>
+        <v>45945.41666666666</v>
       </c>
     </row>
     <row r="5">
@@ -1015,7 +1015,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ibri</t>
+          <t>Sur</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1135,7 +1135,7 @@
         <v>0</v>
       </c>
       <c r="AK5" s="3" t="n">
-        <v>45945.41666666666</v>
+        <v>45945.42361111111</v>
       </c>
     </row>
     <row r="6">
@@ -1144,7 +1144,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Dhofar</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sur</t>
+          <t>Smail</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1264,7 +1264,7 @@
         <v>0</v>
       </c>
       <c r="AK6" s="3" t="n">
-        <v>45945.42361111111</v>
+        <v>45945.47569444445</v>
       </c>
     </row>
     <row r="7">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Dhofar</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Smail</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1393,7 +1393,7 @@
         <v>0</v>
       </c>
       <c r="AK7" s="3" t="n">
-        <v>45945.47569444445</v>
+        <v>45945.5</v>
       </c>
     </row>
     <row r="8">
@@ -1402,12 +1402,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Leopards</t>
+          <t>Al-Rustaq</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bandari</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1522,7 +1522,7 @@
         <v>0</v>
       </c>
       <c r="AK8" s="3" t="n">
-        <v>45945.5</v>
+        <v>45945.52777777778</v>
       </c>
     </row>
     <row r="9">
@@ -1531,12 +1531,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al-Rustaq</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Saham</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>6.53</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1651,7 +1651,7 @@
         <v>0</v>
       </c>
       <c r="AK9" s="3" t="n">
-        <v>45945.52777777778</v>
+        <v>45945.54166666666</v>
       </c>
     </row>
     <row r="10">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Shabana</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Posta Rangers</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,61 +1701,61 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>6.53</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1780,7 +1780,7 @@
         <v>0</v>
       </c>
       <c r="AK10" s="3" t="n">
-        <v>45945.54166666666</v>
+        <v>45945.58333333334</v>
       </c>
     </row>
     <row r="11">
@@ -1789,27 +1789,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Leopards</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Bandari</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>5.07</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>8.57</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="AK11" s="3" t="n">
-        <v>45945.79166666666</v>
+        <v>45945.75</v>
       </c>
     </row>
     <row r="12">
@@ -1918,7 +1918,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,61 +1959,61 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>3.65</v>
+        <v>1.36</v>
       </c>
       <c r="M12" t="n">
-        <v>3.2</v>
+        <v>4.1</v>
       </c>
       <c r="N12" t="n">
-        <v>2.02</v>
+        <v>7.2</v>
       </c>
       <c r="O12" t="n">
-        <v>4.6</v>
+        <v>1.85</v>
       </c>
       <c r="P12" t="n">
-        <v>1.98</v>
+        <v>2.34</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.62</v>
+        <v>7.1</v>
       </c>
       <c r="R12" t="n">
-        <v>1.46</v>
+        <v>1.34</v>
       </c>
       <c r="S12" t="n">
-        <v>2.53</v>
+        <v>2.99</v>
       </c>
       <c r="T12" t="n">
-        <v>3.15</v>
+        <v>2.59</v>
       </c>
       <c r="U12" t="n">
-        <v>1.31</v>
+        <v>1.44</v>
       </c>
       <c r="V12" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="W12" t="n">
-        <v>1.36</v>
+        <v>1.23</v>
       </c>
       <c r="X12" t="n">
-        <v>2.72</v>
+        <v>3.44</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.27</v>
+        <v>1.78</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.66</v>
+        <v>1.92</v>
       </c>
       <c r="AA12" t="n">
-        <v>3.95</v>
+        <v>2.85</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.94</v>
+        <v>2.15</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.77</v>
+        <v>1.68</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.34</v>
+        <v>1.2</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.26</v>
+        <v>2.96</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2038,7 +2038,7 @@
         <v>0</v>
       </c>
       <c r="AK12" s="3" t="n">
-        <v>45945.8125</v>
+        <v>45945.79166666666</v>
       </c>
     </row>
     <row r="13">
@@ -2047,7 +2047,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,61 +2088,61 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.08</v>
+        <v>3.65</v>
       </c>
       <c r="M13" t="n">
-        <v>3.32</v>
+        <v>2.95</v>
       </c>
       <c r="N13" t="n">
-        <v>3.35</v>
+        <v>1.97</v>
       </c>
       <c r="O13" t="n">
-        <v>2.63</v>
+        <v>4.4</v>
       </c>
       <c r="P13" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.9</v>
+        <v>2.74</v>
       </c>
       <c r="R13" t="n">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="S13" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="T13" t="n">
-        <v>2.9</v>
+        <v>3.15</v>
       </c>
       <c r="U13" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W13" t="n">
         <v>1.36</v>
       </c>
-      <c r="V13" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.33</v>
-      </c>
       <c r="X13" t="n">
-        <v>3</v>
+        <v>2.72</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AA13" t="n">
-        <v>3.75</v>
+        <v>3.94</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.83</v>
+        <v>1.93</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.91</v>
+        <v>1.78</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.67</v>
+        <v>1.28</v>
       </c>
       <c r="AI13" t="n">
         <v>0</v>
@@ -2167,7 +2167,7 @@
         <v>0</v>
       </c>
       <c r="AK13" s="3" t="n">
-        <v>45945.83333333334</v>
+        <v>45945.8125</v>
       </c>
     </row>
     <row r="14">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,61 +2217,61 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.34</v>
+        <v>1.99</v>
       </c>
       <c r="M14" t="n">
-        <v>3.18</v>
+        <v>3.11</v>
       </c>
       <c r="N14" t="n">
-        <v>3.2</v>
+        <v>3.39</v>
       </c>
       <c r="O14" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X14" t="n">
         <v>3</v>
       </c>
-      <c r="P14" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Q14" t="n">
+      <c r="Y14" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AA14" t="n">
         <v>3.75</v>
       </c>
-      <c r="R14" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T14" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="X14" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>4.6</v>
-      </c>
       <c r="AB14" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.05</v>
+        <v>1.83</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.7</v>
+        <v>1.91</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2305,7 +2305,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,61 +2346,61 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.14</v>
+        <v>2.24</v>
       </c>
       <c r="M15" t="n">
-        <v>3.14</v>
+        <v>2.84</v>
       </c>
       <c r="N15" t="n">
-        <v>2.99</v>
+        <v>3.12</v>
       </c>
       <c r="O15" t="n">
-        <v>2.86</v>
+        <v>3</v>
       </c>
       <c r="P15" t="n">
-        <v>2.02</v>
+        <v>1.95</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.84</v>
+        <v>3.75</v>
       </c>
       <c r="R15" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="S15" t="n">
-        <v>2.65</v>
+        <v>2.5</v>
       </c>
       <c r="T15" t="n">
-        <v>2.94</v>
+        <v>3.3</v>
       </c>
       <c r="U15" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="V15" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="W15" t="n">
-        <v>1.31</v>
+        <v>1.5</v>
       </c>
       <c r="X15" t="n">
-        <v>2.94</v>
+        <v>2.45</v>
       </c>
       <c r="Y15" t="n">
-        <v>2.12</v>
+        <v>2.5</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.75</v>
+        <v>1.53</v>
       </c>
       <c r="AA15" t="n">
-        <v>3.54</v>
+        <v>4.6</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.81</v>
+        <v>2.05</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.63</v>
+        <v>1.57</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2425,7 +2425,7 @@
         <v>0</v>
       </c>
       <c r="AK15" s="3" t="n">
-        <v>45945.89583333334</v>
+        <v>45945.83333333334</v>
       </c>
     </row>
     <row r="16">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,61 +2475,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.88</v>
+        <v>2.11</v>
       </c>
       <c r="M16" t="n">
-        <v>3.06</v>
+        <v>2.87</v>
       </c>
       <c r="N16" t="n">
-        <v>2.64</v>
+        <v>3.36</v>
       </c>
       <c r="O16" t="n">
-        <v>3.25</v>
+        <v>2.9</v>
       </c>
       <c r="P16" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="R16" t="n">
-        <v>1.44</v>
+        <v>1.56</v>
       </c>
       <c r="S16" t="n">
-        <v>2.5</v>
+        <v>2.34</v>
       </c>
       <c r="T16" t="n">
-        <v>3.3</v>
+        <v>3.58</v>
       </c>
       <c r="U16" t="n">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="V16" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="W16" t="n">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="X16" t="n">
         <v>2.5</v>
       </c>
       <c r="Y16" t="n">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AA16" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="AC16" t="n">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.75</v>
+        <v>1.64</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,61 +2604,61 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.21</v>
+        <v>2.47</v>
       </c>
       <c r="M17" t="n">
-        <v>3.05</v>
+        <v>2.93</v>
       </c>
       <c r="N17" t="n">
-        <v>3.35</v>
+        <v>2.68</v>
       </c>
       <c r="O17" t="n">
-        <v>2.9</v>
+        <v>3.25</v>
       </c>
       <c r="P17" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.4</v>
+        <v>3.4</v>
       </c>
       <c r="R17" t="n">
-        <v>1.56</v>
+        <v>1.44</v>
       </c>
       <c r="S17" t="n">
-        <v>2.34</v>
+        <v>2.5</v>
       </c>
       <c r="T17" t="n">
-        <v>3.58</v>
+        <v>3.4</v>
       </c>
       <c r="U17" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="V17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="W17" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X17" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Z17" t="n">
         <v>1.55</v>
       </c>
-      <c r="X17" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>1.43</v>
-      </c>
       <c r="AA17" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.13</v>
+        <v>2.09</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.67</v>
+        <v>1.4</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2692,12 +2692,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,85 +2733,214 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.4</v>
+        <v>2.14</v>
       </c>
       <c r="M18" t="n">
-        <v>3.1</v>
+        <v>3.14</v>
       </c>
       <c r="N18" t="n">
-        <v>2.7</v>
+        <v>2.99</v>
       </c>
       <c r="O18" t="n">
-        <v>2.96</v>
+        <v>2.86</v>
       </c>
       <c r="P18" t="n">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.3</v>
+        <v>3.84</v>
       </c>
       <c r="R18" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="U18" t="n">
         <v>1.35</v>
-      </c>
-      <c r="S18" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.39</v>
       </c>
       <c r="V18" t="n">
         <v>1.02</v>
       </c>
       <c r="W18" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="X18" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG18" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK18" s="3" t="n">
+        <v>45945.89583333334</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="n">
+        <v>45945</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>USA USL Championship</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Orange County SC</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>San Antonio</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L19" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="M19" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="N19" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="O19" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W19" t="n">
         <v>1.25</v>
       </c>
-      <c r="X18" t="n">
+      <c r="X19" t="n">
         <v>3.28</v>
       </c>
-      <c r="Y18" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AA18" t="n">
+      <c r="Y19" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AA19" t="n">
         <v>3.14</v>
       </c>
-      <c r="AB18" t="n">
+      <c r="AB19" t="n">
         <v>1.27</v>
       </c>
-      <c r="AC18" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AE18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG18" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK18" s="3" t="n">
+      <c r="AC19" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG19" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK19" s="3" t="n">
         <v>45945.95833333334</v>
       </c>
     </row>

--- a/jogos_2025-10-15.xlsx
+++ b/jogos_2025-10-15.xlsx
@@ -628,7 +628,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Homeboyz</t>
+          <t>Shabana</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bidco United</t>
+          <t>Posta Rangers</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -748,7 +748,7 @@
         <v>0</v>
       </c>
       <c r="AK2" s="3" t="n">
-        <v>45945.375</v>
+        <v>45945.33333333334</v>
       </c>
     </row>
     <row r="3">
@@ -886,12 +886,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>Homeboyz</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ibri</t>
+          <t>Bidco United</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1006,7 +1006,7 @@
         <v>0</v>
       </c>
       <c r="AK4" s="3" t="n">
-        <v>45945.41666666666</v>
+        <v>45945.375</v>
       </c>
     </row>
     <row r="5">
@@ -1015,7 +1015,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sur</t>
+          <t>Ibri</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1135,7 +1135,7 @@
         <v>0</v>
       </c>
       <c r="AK5" s="3" t="n">
-        <v>45945.42361111111</v>
+        <v>45945.41666666666</v>
       </c>
     </row>
     <row r="6">
@@ -1144,7 +1144,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Dhofar</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Smail</t>
+          <t>Sur</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,13 +1185,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1224,10 +1224,10 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AA6" t="n">
         <v>0</v>
@@ -1264,7 +1264,7 @@
         <v>0</v>
       </c>
       <c r="AK6" s="3" t="n">
-        <v>45945.47569444445</v>
+        <v>45945.42361111111</v>
       </c>
     </row>
     <row r="7">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Dhofar</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Smail</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1393,7 +1393,7 @@
         <v>0</v>
       </c>
       <c r="AK7" s="3" t="n">
-        <v>45945.5</v>
+        <v>45945.47569444445</v>
       </c>
     </row>
     <row r="8">
@@ -1402,12 +1402,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Al-Rustaq</t>
+          <t>Leopards</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Saham</t>
+          <t>Bandari</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1522,7 +1522,7 @@
         <v>0</v>
       </c>
       <c r="AK8" s="3" t="n">
-        <v>45945.52777777778</v>
+        <v>45945.5</v>
       </c>
     </row>
     <row r="9">
@@ -1531,12 +1531,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>6.53</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1651,7 +1651,7 @@
         <v>0</v>
       </c>
       <c r="AK9" s="3" t="n">
-        <v>45945.54166666666</v>
+        <v>45945.5</v>
       </c>
     </row>
     <row r="10">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Shabana</t>
+          <t>Al-Rustaq</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Posta Rangers</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1780,7 +1780,7 @@
         <v>0</v>
       </c>
       <c r="AK10" s="3" t="n">
-        <v>45945.58333333334</v>
+        <v>45945.52777777778</v>
       </c>
     </row>
     <row r="11">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Leopards</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bandari</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>6.53</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="AK11" s="3" t="n">
-        <v>45945.75</v>
+        <v>45945.54166666666</v>
       </c>
     </row>
     <row r="12">
@@ -1971,10 +1971,10 @@
         <v>1.85</v>
       </c>
       <c r="P12" t="n">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="Q12" t="n">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="R12" t="n">
         <v>1.34</v>
@@ -1983,19 +1983,19 @@
         <v>2.99</v>
       </c>
       <c r="T12" t="n">
-        <v>2.59</v>
+        <v>2.6</v>
       </c>
       <c r="U12" t="n">
         <v>1.44</v>
       </c>
       <c r="V12" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="W12" t="n">
         <v>1.23</v>
       </c>
       <c r="X12" t="n">
-        <v>3.44</v>
+        <v>3.95</v>
       </c>
       <c r="Y12" t="n">
         <v>1.78</v>
@@ -2007,13 +2007,13 @@
         <v>2.85</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.15</v>
+        <v>2.08</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         <v>1.2</v>
       </c>
       <c r="AH12" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2097,7 +2097,7 @@
         <v>1.97</v>
       </c>
       <c r="O13" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="P13" t="n">
         <v>1.95</v>
@@ -2106,19 +2106,19 @@
         <v>2.74</v>
       </c>
       <c r="R13" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="S13" t="n">
         <v>2.5</v>
       </c>
       <c r="T13" t="n">
-        <v>3.15</v>
+        <v>3.39</v>
       </c>
       <c r="U13" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="V13" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="W13" t="n">
         <v>1.36</v>
@@ -2133,7 +2133,7 @@
         <v>1.65</v>
       </c>
       <c r="AA13" t="n">
-        <v>3.94</v>
+        <v>4.3</v>
       </c>
       <c r="AB13" t="n">
         <v>1.18</v>
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,61 +2217,61 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.99</v>
+        <v>2.24</v>
       </c>
       <c r="M14" t="n">
-        <v>3.11</v>
+        <v>2.84</v>
       </c>
       <c r="N14" t="n">
-        <v>3.39</v>
+        <v>3.12</v>
       </c>
       <c r="O14" t="n">
-        <v>2.63</v>
+        <v>3</v>
       </c>
       <c r="P14" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="R14" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="S14" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="T14" t="n">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="U14" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="V14" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="W14" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="X14" t="n">
-        <v>3</v>
+        <v>2.45</v>
       </c>
       <c r="Y14" t="n">
-        <v>2.12</v>
+        <v>2.5</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.72</v>
+        <v>1.53</v>
       </c>
       <c r="AA14" t="n">
-        <v>3.75</v>
+        <v>4.6</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.91</v>
+        <v>1.7</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2287,7 +2287,7 @@
         <v>1.33</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,61 +2346,61 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.24</v>
+        <v>1.99</v>
       </c>
       <c r="M15" t="n">
-        <v>2.84</v>
+        <v>3.11</v>
       </c>
       <c r="N15" t="n">
-        <v>3.12</v>
+        <v>3.39</v>
       </c>
       <c r="O15" t="n">
-        <v>3</v>
+        <v>2.62</v>
       </c>
       <c r="P15" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="R15" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="S15" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="T15" t="n">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="U15" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="V15" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="W15" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="X15" t="n">
-        <v>2.45</v>
+        <v>3.2</v>
       </c>
       <c r="Y15" t="n">
-        <v>2.5</v>
+        <v>2.12</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.53</v>
+        <v>1.72</v>
       </c>
       <c r="AA15" t="n">
-        <v>4.6</v>
+        <v>3.54</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.05</v>
+        <v>1.87</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.7</v>
+        <v>1.91</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,61 +2475,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.11</v>
+        <v>2.14</v>
       </c>
       <c r="M16" t="n">
-        <v>2.87</v>
+        <v>3.14</v>
       </c>
       <c r="N16" t="n">
-        <v>3.36</v>
+        <v>2.99</v>
       </c>
       <c r="O16" t="n">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="P16" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="Q16" t="n">
         <v>4</v>
       </c>
       <c r="R16" t="n">
-        <v>1.56</v>
+        <v>1.42</v>
       </c>
       <c r="S16" t="n">
-        <v>2.34</v>
+        <v>2.65</v>
       </c>
       <c r="T16" t="n">
-        <v>3.58</v>
+        <v>3.21</v>
       </c>
       <c r="U16" t="n">
-        <v>1.23</v>
+        <v>1.35</v>
       </c>
       <c r="V16" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="W16" t="n">
         <v>1.55</v>
       </c>
       <c r="X16" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="Y16" t="n">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="AA16" t="n">
-        <v>4.9</v>
+        <v>3.54</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.11</v>
+        <v>1.22</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.13</v>
+        <v>1.81</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.64</v>
+        <v>1.9</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,61 +2604,61 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.47</v>
+        <v>2.11</v>
       </c>
       <c r="M17" t="n">
-        <v>2.93</v>
+        <v>2.87</v>
       </c>
       <c r="N17" t="n">
-        <v>2.68</v>
+        <v>3.36</v>
       </c>
       <c r="O17" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="P17" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="R17" t="n">
-        <v>1.44</v>
+        <v>1.56</v>
       </c>
       <c r="S17" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="X17" t="n">
         <v>2.5</v>
       </c>
-      <c r="T17" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="X17" t="n">
-        <v>2.45</v>
-      </c>
       <c r="Y17" t="n">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.55</v>
+        <v>1.45</v>
       </c>
       <c r="AA17" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.09</v>
+        <v>2.13</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.75</v>
+        <v>1.64</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,40 +2733,40 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.14</v>
+        <v>2.47</v>
       </c>
       <c r="M18" t="n">
-        <v>3.14</v>
+        <v>2.93</v>
       </c>
       <c r="N18" t="n">
-        <v>2.99</v>
+        <v>2.68</v>
       </c>
       <c r="O18" t="n">
-        <v>2.86</v>
+        <v>3.25</v>
       </c>
       <c r="P18" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.84</v>
+        <v>3.4</v>
       </c>
       <c r="R18" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="S18" t="n">
-        <v>2.65</v>
+        <v>2.5</v>
       </c>
       <c r="T18" t="n">
-        <v>2.94</v>
+        <v>3.4</v>
       </c>
       <c r="U18" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="V18" t="n">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="W18" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="X18" t="n">
         <v>2.45</v>
@@ -2775,19 +2775,19 @@
         <v>2.45</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AA18" t="n">
-        <v>3.54</v>
+        <v>4.55</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.81</v>
+        <v>2.09</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.9</v>
+        <v>1.75</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.63</v>
+        <v>1.4</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>

--- a/jogos_2025-10-15.xlsx
+++ b/jogos_2025-10-15.xlsx
@@ -628,7 +628,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Shabana</t>
+          <t>Murang'a SEAL</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Posta Rangers</t>
+          <t>Sofapaka</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -748,7 +748,7 @@
         <v>0</v>
       </c>
       <c r="AK2" s="3" t="n">
-        <v>45945.33333333334</v>
+        <v>45945.375</v>
       </c>
     </row>
     <row r="3">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Murang'a SEAL</t>
+          <t>Homeboyz</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sofapaka</t>
+          <t>Bidco United</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -886,12 +886,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Homeboyz</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bidco United</t>
+          <t>Ibri</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1006,7 +1006,7 @@
         <v>0</v>
       </c>
       <c r="AK4" s="3" t="n">
-        <v>45945.375</v>
+        <v>45945.41666666666</v>
       </c>
     </row>
     <row r="5">
@@ -1015,7 +1015,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ibri</t>
+          <t>Sur</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,13 +1056,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1095,10 +1095,10 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AA5" t="n">
         <v>0</v>
@@ -1135,7 +1135,7 @@
         <v>0</v>
       </c>
       <c r="AK5" s="3" t="n">
-        <v>45945.41666666666</v>
+        <v>45945.42361111111</v>
       </c>
     </row>
     <row r="6">
@@ -1144,7 +1144,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Dhofar</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sur</t>
+          <t>Smail</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,13 +1185,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1224,10 +1224,10 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
         <v>0</v>
@@ -1264,7 +1264,7 @@
         <v>0</v>
       </c>
       <c r="AK6" s="3" t="n">
-        <v>45945.42361111111</v>
+        <v>45945.47569444445</v>
       </c>
     </row>
     <row r="7">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Dhofar</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Smail</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1393,7 +1393,7 @@
         <v>0</v>
       </c>
       <c r="AK7" s="3" t="n">
-        <v>45945.47569444445</v>
+        <v>45945.5</v>
       </c>
     </row>
     <row r="8">
@@ -1402,12 +1402,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Leopards</t>
+          <t>Al-Rustaq</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bandari</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1522,7 +1522,7 @@
         <v>0</v>
       </c>
       <c r="AK8" s="3" t="n">
-        <v>45945.5</v>
+        <v>45945.52777777778</v>
       </c>
     </row>
     <row r="9">
@@ -1531,12 +1531,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>6.53</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1651,7 +1651,7 @@
         <v>0</v>
       </c>
       <c r="AK9" s="3" t="n">
-        <v>45945.5</v>
+        <v>45945.54166666666</v>
       </c>
     </row>
     <row r="10">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al-Rustaq</t>
+          <t>Shabana</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Saham</t>
+          <t>Posta Rangers</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1780,7 +1780,7 @@
         <v>0</v>
       </c>
       <c r="AK10" s="3" t="n">
-        <v>45945.52777777778</v>
+        <v>45945.58333333334</v>
       </c>
     </row>
     <row r="11">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Leopards</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Bandari</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>6.53</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="AK11" s="3" t="n">
-        <v>45945.54166666666</v>
+        <v>45945.75</v>
       </c>
     </row>
     <row r="12">
@@ -1962,10 +1962,10 @@
         <v>1.36</v>
       </c>
       <c r="M12" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="N12" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="O12" t="n">
         <v>1.85</v>
@@ -1989,25 +1989,25 @@
         <v>1.44</v>
       </c>
       <c r="V12" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W12" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="X12" t="n">
-        <v>3.95</v>
+        <v>3.52</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.78</v>
+        <v>1.84</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.85</v>
+        <v>3.14</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AC12" t="n">
         <v>2.08</v>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AH12" t="n">
-        <v>3</v>
+        <v>3.02</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>3.65</v>
+        <v>3.45</v>
       </c>
       <c r="M13" t="n">
-        <v>2.95</v>
+        <v>3.15</v>
       </c>
       <c r="N13" t="n">
-        <v>1.97</v>
+        <v>2.05</v>
       </c>
       <c r="O13" t="n">
         <v>4</v>
@@ -2103,7 +2103,7 @@
         <v>1.95</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.74</v>
+        <v>2.73</v>
       </c>
       <c r="R13" t="n">
         <v>1.48</v>
@@ -2127,22 +2127,22 @@
         <v>2.72</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AA13" t="n">
-        <v>4.3</v>
+        <v>3.94</v>
       </c>
       <c r="AB13" t="n">
         <v>1.18</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2217,13 +2217,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="M14" t="n">
-        <v>2.84</v>
+        <v>3.1</v>
       </c>
       <c r="N14" t="n">
-        <v>3.12</v>
+        <v>3.2</v>
       </c>
       <c r="O14" t="n">
         <v>3</v>
@@ -2241,7 +2241,7 @@
         <v>2.5</v>
       </c>
       <c r="T14" t="n">
-        <v>3.3</v>
+        <v>3.48</v>
       </c>
       <c r="U14" t="n">
         <v>1.3</v>
@@ -2250,13 +2250,13 @@
         <v>1.08</v>
       </c>
       <c r="W14" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="X14" t="n">
-        <v>2.45</v>
+        <v>2.59</v>
       </c>
       <c r="Y14" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="Z14" t="n">
         <v>1.53</v>
@@ -2287,7 +2287,7 @@
         <v>1.33</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2346,13 +2346,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.99</v>
+        <v>2.11</v>
       </c>
       <c r="M15" t="n">
-        <v>3.11</v>
+        <v>3.25</v>
       </c>
       <c r="N15" t="n">
-        <v>3.39</v>
+        <v>3.46</v>
       </c>
       <c r="O15" t="n">
         <v>2.62</v>
@@ -2382,13 +2382,13 @@
         <v>1.33</v>
       </c>
       <c r="X15" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="Y15" t="n">
         <v>2.12</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AA15" t="n">
         <v>3.54</v>
@@ -2505,19 +2505,19 @@
         <v>1.35</v>
       </c>
       <c r="V16" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="W16" t="n">
-        <v>1.55</v>
+        <v>1.34</v>
       </c>
       <c r="X16" t="n">
-        <v>2.45</v>
+        <v>3.25</v>
       </c>
       <c r="Y16" t="n">
-        <v>2.45</v>
+        <v>2.19</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="AA16" t="n">
         <v>3.54</v>
@@ -2604,13 +2604,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="M17" t="n">
-        <v>2.87</v>
+        <v>3</v>
       </c>
       <c r="N17" t="n">
-        <v>3.36</v>
+        <v>3.35</v>
       </c>
       <c r="O17" t="n">
         <v>3</v>
@@ -2637,19 +2637,19 @@
         <v>1.09</v>
       </c>
       <c r="W17" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="X17" t="n">
         <v>2.5</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.55</v>
+        <v>2.67</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="AA17" t="n">
-        <v>4.9</v>
+        <v>5.32</v>
       </c>
       <c r="AB17" t="n">
         <v>1.11</v>
@@ -2733,13 +2733,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.47</v>
+        <v>2.86</v>
       </c>
       <c r="M18" t="n">
-        <v>2.93</v>
+        <v>3.05</v>
       </c>
       <c r="N18" t="n">
-        <v>2.68</v>
+        <v>2.5</v>
       </c>
       <c r="O18" t="n">
         <v>3.25</v>
@@ -2748,7 +2748,7 @@
         <v>2</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.4</v>
+        <v>3.32</v>
       </c>
       <c r="R18" t="n">
         <v>1.44</v>
@@ -2766,16 +2766,16 @@
         <v>1.1</v>
       </c>
       <c r="W18" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="X18" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Z18" t="n">
         <v>1.5</v>
-      </c>
-      <c r="X18" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>1.55</v>
       </c>
       <c r="AA18" t="n">
         <v>4.55</v>

--- a/jogos_2025-10-15.xlsx
+++ b/jogos_2025-10-15.xlsx
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Murang'a SEAL</t>
+          <t>Homeboyz</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sofapaka</t>
+          <t>Bidco United</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Homeboyz</t>
+          <t>Murang'a SEAL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bidco United</t>
+          <t>Sofapaka</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1962,10 +1962,10 @@
         <v>1.36</v>
       </c>
       <c r="M12" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="N12" t="n">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="O12" t="n">
         <v>1.85</v>
@@ -1998,10 +1998,10 @@
         <v>3.52</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.84</v>
+        <v>1.78</v>
       </c>
       <c r="Z12" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AA12" t="n">
         <v>3.14</v>
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>3.45</v>
+        <v>3.65</v>
       </c>
       <c r="M13" t="n">
-        <v>3.15</v>
+        <v>2.95</v>
       </c>
       <c r="N13" t="n">
-        <v>2.05</v>
+        <v>1.97</v>
       </c>
       <c r="O13" t="n">
         <v>4</v>
@@ -2127,10 +2127,10 @@
         <v>2.72</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AA13" t="n">
         <v>3.94</v>
@@ -2217,13 +2217,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="M14" t="n">
-        <v>3.1</v>
+        <v>2.84</v>
       </c>
       <c r="N14" t="n">
-        <v>3.2</v>
+        <v>3.12</v>
       </c>
       <c r="O14" t="n">
         <v>3</v>
@@ -2250,13 +2250,13 @@
         <v>1.08</v>
       </c>
       <c r="W14" t="n">
-        <v>1.46</v>
+        <v>1.52</v>
       </c>
       <c r="X14" t="n">
-        <v>2.59</v>
+        <v>2.35</v>
       </c>
       <c r="Y14" t="n">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="Z14" t="n">
         <v>1.53</v>
@@ -2346,13 +2346,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.11</v>
+        <v>1.99</v>
       </c>
       <c r="M15" t="n">
-        <v>3.25</v>
+        <v>3.11</v>
       </c>
       <c r="N15" t="n">
-        <v>3.46</v>
+        <v>3.39</v>
       </c>
       <c r="O15" t="n">
         <v>2.62</v>
@@ -2388,7 +2388,7 @@
         <v>2.12</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AA15" t="n">
         <v>3.54</v>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,61 +2475,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.14</v>
+        <v>2.11</v>
       </c>
       <c r="M16" t="n">
-        <v>3.14</v>
+        <v>2.87</v>
       </c>
       <c r="N16" t="n">
-        <v>2.99</v>
+        <v>3.36</v>
       </c>
       <c r="O16" t="n">
-        <v>2.86</v>
+        <v>3</v>
       </c>
       <c r="P16" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="Q16" t="n">
         <v>4</v>
       </c>
       <c r="R16" t="n">
-        <v>1.42</v>
+        <v>1.56</v>
       </c>
       <c r="S16" t="n">
-        <v>2.65</v>
+        <v>2.34</v>
       </c>
       <c r="T16" t="n">
-        <v>3.21</v>
+        <v>3.5</v>
       </c>
       <c r="U16" t="n">
-        <v>1.35</v>
+        <v>1.23</v>
       </c>
       <c r="V16" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="W16" t="n">
-        <v>1.34</v>
+        <v>1.55</v>
       </c>
       <c r="X16" t="n">
-        <v>3.25</v>
+        <v>2.5</v>
       </c>
       <c r="Y16" t="n">
-        <v>2.19</v>
+        <v>2.4</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="AA16" t="n">
-        <v>3.54</v>
+        <v>5.32</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.22</v>
+        <v>1.11</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.81</v>
+        <v>2.13</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.9</v>
+        <v>1.64</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,61 +2604,61 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="M17" t="n">
-        <v>3</v>
+        <v>3.14</v>
       </c>
       <c r="N17" t="n">
-        <v>3.35</v>
+        <v>2.99</v>
       </c>
       <c r="O17" t="n">
-        <v>3</v>
+        <v>2.86</v>
       </c>
       <c r="P17" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="Q17" t="n">
         <v>4</v>
       </c>
       <c r="R17" t="n">
-        <v>1.56</v>
+        <v>1.42</v>
       </c>
       <c r="S17" t="n">
-        <v>2.34</v>
+        <v>2.65</v>
       </c>
       <c r="T17" t="n">
-        <v>3.5</v>
+        <v>3.21</v>
       </c>
       <c r="U17" t="n">
-        <v>1.23</v>
+        <v>1.35</v>
       </c>
       <c r="V17" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="W17" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="X17" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.67</v>
+        <v>1.98</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.43</v>
+        <v>1.73</v>
       </c>
       <c r="AA17" t="n">
-        <v>5.32</v>
+        <v>3.54</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.11</v>
+        <v>1.22</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.13</v>
+        <v>1.81</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.64</v>
+        <v>1.9</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2733,13 +2733,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.86</v>
+        <v>2.47</v>
       </c>
       <c r="M18" t="n">
-        <v>3.05</v>
+        <v>2.93</v>
       </c>
       <c r="N18" t="n">
-        <v>2.5</v>
+        <v>2.68</v>
       </c>
       <c r="O18" t="n">
         <v>3.25</v>
@@ -2766,16 +2766,16 @@
         <v>1.1</v>
       </c>
       <c r="W18" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="X18" t="n">
-        <v>2.65</v>
+        <v>2.45</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AA18" t="n">
         <v>4.55</v>
@@ -2871,7 +2871,7 @@
         <v>2.55</v>
       </c>
       <c r="O19" t="n">
-        <v>2.94</v>
+        <v>2.93</v>
       </c>
       <c r="P19" t="n">
         <v>2.1</v>
@@ -2889,13 +2889,13 @@
         <v>2.7</v>
       </c>
       <c r="U19" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="V19" t="n">
         <v>1.01</v>
       </c>
       <c r="W19" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="X19" t="n">
         <v>3.28</v>
@@ -2910,10 +2910,10 @@
         <v>3.14</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="AD19" t="n">
         <v>2</v>
@@ -2929,7 +2929,7 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.27</v>
+        <v>1.39</v>
       </c>
       <c r="AH19" t="n">
         <v>1.51</v>

--- a/jogos_2025-10-15.xlsx
+++ b/jogos_2025-10-15.xlsx
@@ -628,7 +628,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Homeboyz</t>
+          <t>Shabana</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bidco United</t>
+          <t>Posta Rangers</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -748,7 +748,7 @@
         <v>0</v>
       </c>
       <c r="AK2" s="3" t="n">
-        <v>45945.375</v>
+        <v>45945.33333333334</v>
       </c>
     </row>
     <row r="3">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Murang'a SEAL</t>
+          <t>Homeboyz</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sofapaka</t>
+          <t>Bidco United</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -886,12 +886,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>Murang'a SEAL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ibri</t>
+          <t>Sofapaka</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1006,7 +1006,7 @@
         <v>0</v>
       </c>
       <c r="AK4" s="3" t="n">
-        <v>45945.41666666666</v>
+        <v>45945.375</v>
       </c>
     </row>
     <row r="5">
@@ -1015,7 +1015,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sur</t>
+          <t>Ibri</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,13 +1056,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1095,10 +1095,10 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
         <v>0</v>
@@ -1135,7 +1135,7 @@
         <v>0</v>
       </c>
       <c r="AK5" s="3" t="n">
-        <v>45945.42361111111</v>
+        <v>45945.41666666666</v>
       </c>
     </row>
     <row r="6">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Dhofar</t>
+          <t>Leopards</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Smail</t>
+          <t>Bandari</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1264,7 +1264,7 @@
         <v>0</v>
       </c>
       <c r="AK6" s="3" t="n">
-        <v>45945.47569444445</v>
+        <v>45945.41666666666</v>
       </c>
     </row>
     <row r="7">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Sur</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,13 +1314,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1353,10 +1353,10 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
@@ -1393,7 +1393,7 @@
         <v>0</v>
       </c>
       <c r="AK7" s="3" t="n">
-        <v>45945.5</v>
+        <v>45945.42361111111</v>
       </c>
     </row>
     <row r="8">
@@ -1402,7 +1402,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Al-Rustaq</t>
+          <t>Dhofar</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Saham</t>
+          <t>Smail</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1522,7 +1522,7 @@
         <v>0</v>
       </c>
       <c r="AK8" s="3" t="n">
-        <v>45945.52777777778</v>
+        <v>45945.47569444445</v>
       </c>
     </row>
     <row r="9">
@@ -1531,12 +1531,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>6.53</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1651,7 +1651,7 @@
         <v>0</v>
       </c>
       <c r="AK9" s="3" t="n">
-        <v>45945.54166666666</v>
+        <v>45945.5</v>
       </c>
     </row>
     <row r="10">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Shabana</t>
+          <t>Al-Rustaq</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Posta Rangers</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1780,7 +1780,7 @@
         <v>0</v>
       </c>
       <c r="AK10" s="3" t="n">
-        <v>45945.58333333334</v>
+        <v>45945.52777777778</v>
       </c>
     </row>
     <row r="11">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Leopards</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bandari</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>6.53</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="AK11" s="3" t="n">
-        <v>45945.75</v>
+        <v>45945.54166666666</v>
       </c>
     </row>
     <row r="12">
@@ -1962,28 +1962,28 @@
         <v>1.36</v>
       </c>
       <c r="M12" t="n">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="N12" t="n">
-        <v>7.2</v>
+        <v>8.5</v>
       </c>
       <c r="O12" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="P12" t="n">
         <v>2.38</v>
       </c>
       <c r="Q12" t="n">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="R12" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="S12" t="n">
-        <v>2.99</v>
+        <v>3.02</v>
       </c>
       <c r="T12" t="n">
-        <v>2.6</v>
+        <v>2.59</v>
       </c>
       <c r="U12" t="n">
         <v>1.44</v>
@@ -1998,13 +1998,13 @@
         <v>3.52</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.78</v>
+        <v>1.86</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.92</v>
+        <v>1.99</v>
       </c>
       <c r="AA12" t="n">
-        <v>3.14</v>
+        <v>2.85</v>
       </c>
       <c r="AB12" t="n">
         <v>1.33</v>
@@ -2088,40 +2088,40 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>3.65</v>
+        <v>3.89</v>
       </c>
       <c r="M13" t="n">
-        <v>2.95</v>
+        <v>3.3</v>
       </c>
       <c r="N13" t="n">
-        <v>1.97</v>
+        <v>2.05</v>
       </c>
       <c r="O13" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="P13" t="n">
         <v>1.95</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.73</v>
+        <v>2.74</v>
       </c>
       <c r="R13" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="S13" t="n">
         <v>2.5</v>
       </c>
       <c r="T13" t="n">
-        <v>3.39</v>
+        <v>3.15</v>
       </c>
       <c r="U13" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="V13" t="n">
         <v>1.06</v>
       </c>
       <c r="W13" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="X13" t="n">
         <v>2.72</v>
@@ -2130,19 +2130,19 @@
         <v>2.25</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AA13" t="n">
-        <v>3.94</v>
+        <v>4.25</v>
       </c>
       <c r="AB13" t="n">
         <v>1.18</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2217,16 +2217,16 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.24</v>
+        <v>2.35</v>
       </c>
       <c r="M14" t="n">
-        <v>2.84</v>
+        <v>3.1</v>
       </c>
       <c r="N14" t="n">
-        <v>3.12</v>
+        <v>3.31</v>
       </c>
       <c r="O14" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="P14" t="n">
         <v>1.95</v>
@@ -2241,7 +2241,7 @@
         <v>2.5</v>
       </c>
       <c r="T14" t="n">
-        <v>3.48</v>
+        <v>3.3</v>
       </c>
       <c r="U14" t="n">
         <v>1.3</v>
@@ -2250,13 +2250,13 @@
         <v>1.08</v>
       </c>
       <c r="W14" t="n">
-        <v>1.52</v>
+        <v>1.44</v>
       </c>
       <c r="X14" t="n">
-        <v>2.35</v>
+        <v>2.63</v>
       </c>
       <c r="Y14" t="n">
-        <v>2.5</v>
+        <v>2.51</v>
       </c>
       <c r="Z14" t="n">
         <v>1.53</v>
@@ -2268,10 +2268,10 @@
         <v>1.17</v>
       </c>
       <c r="AC14" t="n">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2346,22 +2346,22 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.99</v>
+        <v>2.1</v>
       </c>
       <c r="M15" t="n">
-        <v>3.11</v>
+        <v>3</v>
       </c>
       <c r="N15" t="n">
-        <v>3.39</v>
+        <v>3.52</v>
       </c>
       <c r="O15" t="n">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="P15" t="n">
         <v>2.1</v>
       </c>
       <c r="Q15" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="R15" t="n">
         <v>1.4</v>
@@ -2385,10 +2385,10 @@
         <v>3</v>
       </c>
       <c r="Y15" t="n">
-        <v>2.12</v>
+        <v>2.05</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AA15" t="n">
         <v>3.54</v>
@@ -2397,7 +2397,7 @@
         <v>1.25</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="AD15" t="n">
         <v>1.91</v>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,40 +2475,40 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.11</v>
+        <v>2.91</v>
       </c>
       <c r="M16" t="n">
-        <v>2.87</v>
+        <v>3.12</v>
       </c>
       <c r="N16" t="n">
-        <v>3.36</v>
+        <v>2.53</v>
       </c>
       <c r="O16" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="P16" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="Q16" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="R16" t="n">
-        <v>1.56</v>
+        <v>1.44</v>
       </c>
       <c r="S16" t="n">
-        <v>2.34</v>
+        <v>2.5</v>
       </c>
       <c r="T16" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="U16" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="V16" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="W16" t="n">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="X16" t="n">
         <v>2.5</v>
@@ -2520,16 +2520,16 @@
         <v>1.5</v>
       </c>
       <c r="AA16" t="n">
-        <v>5.32</v>
+        <v>4.8</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.67</v>
+        <v>1.4</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2616,10 +2616,10 @@
         <v>2.86</v>
       </c>
       <c r="P17" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="Q17" t="n">
-        <v>4</v>
+        <v>3.84</v>
       </c>
       <c r="R17" t="n">
         <v>1.42</v>
@@ -2628,25 +2628,25 @@
         <v>2.65</v>
       </c>
       <c r="T17" t="n">
-        <v>3.21</v>
+        <v>2.94</v>
       </c>
       <c r="U17" t="n">
         <v>1.35</v>
       </c>
       <c r="V17" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="W17" t="n">
-        <v>1.55</v>
+        <v>1.31</v>
       </c>
       <c r="X17" t="n">
-        <v>2.45</v>
+        <v>2.94</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.98</v>
+        <v>2.12</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AA17" t="n">
         <v>3.54</v>
@@ -2655,10 +2655,10 @@
         <v>1.22</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,61 +2733,61 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.47</v>
+        <v>2.2</v>
       </c>
       <c r="M18" t="n">
-        <v>2.93</v>
+        <v>3.1</v>
       </c>
       <c r="N18" t="n">
-        <v>2.68</v>
+        <v>3.5</v>
       </c>
       <c r="O18" t="n">
-        <v>3.25</v>
+        <v>2.9</v>
       </c>
       <c r="P18" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.32</v>
+        <v>4.4</v>
       </c>
       <c r="R18" t="n">
-        <v>1.44</v>
+        <v>1.56</v>
       </c>
       <c r="S18" t="n">
-        <v>2.5</v>
+        <v>2.34</v>
       </c>
       <c r="T18" t="n">
-        <v>3.4</v>
+        <v>3.58</v>
       </c>
       <c r="U18" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="V18" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="W18" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="X18" t="n">
-        <v>2.45</v>
+        <v>2.53</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.45</v>
+        <v>2.48</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.55</v>
+        <v>1.43</v>
       </c>
       <c r="AA18" t="n">
-        <v>4.55</v>
+        <v>4.9</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.09</v>
+        <v>2.23</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.75</v>
+        <v>1.64</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
@@ -2862,22 +2862,22 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="M19" t="n">
-        <v>3.6</v>
+        <v>3.58</v>
       </c>
       <c r="N19" t="n">
-        <v>2.55</v>
+        <v>2.7</v>
       </c>
       <c r="O19" t="n">
-        <v>2.93</v>
+        <v>2.92</v>
       </c>
       <c r="P19" t="n">
         <v>2.1</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.2</v>
+        <v>3.46</v>
       </c>
       <c r="R19" t="n">
         <v>1.35</v>
@@ -2889,34 +2889,34 @@
         <v>2.7</v>
       </c>
       <c r="U19" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="V19" t="n">
         <v>1.01</v>
       </c>
       <c r="W19" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="X19" t="n">
         <v>3.28</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AA19" t="n">
         <v>3.14</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="AC19" t="n">
         <v>1.69</v>
       </c>
       <c r="AD19" t="n">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2929,7 +2929,7 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.39</v>
+        <v>1.27</v>
       </c>
       <c r="AH19" t="n">
         <v>1.51</v>

--- a/jogos_2025-10-15.xlsx
+++ b/jogos_2025-10-15.xlsx
@@ -1962,25 +1962,25 @@
         <v>1.36</v>
       </c>
       <c r="M12" t="n">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="N12" t="n">
-        <v>8.5</v>
+        <v>7.2</v>
       </c>
       <c r="O12" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="P12" t="n">
         <v>2.38</v>
       </c>
       <c r="Q12" t="n">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="R12" t="n">
         <v>1.33</v>
       </c>
       <c r="S12" t="n">
-        <v>3.02</v>
+        <v>3.04</v>
       </c>
       <c r="T12" t="n">
         <v>2.59</v>
@@ -1995,13 +1995,13 @@
         <v>1.22</v>
       </c>
       <c r="X12" t="n">
-        <v>3.52</v>
+        <v>3.54</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.86</v>
+        <v>1.78</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.99</v>
+        <v>1.92</v>
       </c>
       <c r="AA12" t="n">
         <v>2.85</v>
@@ -2010,10 +2010,10 @@
         <v>1.33</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>3.89</v>
+        <v>3.65</v>
       </c>
       <c r="M13" t="n">
-        <v>3.3</v>
+        <v>2.95</v>
       </c>
       <c r="N13" t="n">
-        <v>2.05</v>
+        <v>1.97</v>
       </c>
       <c r="O13" t="n">
         <v>4.4</v>
@@ -2118,10 +2118,10 @@
         <v>1.31</v>
       </c>
       <c r="V13" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="W13" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="X13" t="n">
         <v>2.72</v>
@@ -2130,10 +2130,10 @@
         <v>2.25</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AA13" t="n">
-        <v>4.25</v>
+        <v>3.94</v>
       </c>
       <c r="AB13" t="n">
         <v>1.18</v>
@@ -2217,16 +2217,16 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.35</v>
+        <v>2.24</v>
       </c>
       <c r="M14" t="n">
-        <v>3.1</v>
+        <v>2.84</v>
       </c>
       <c r="N14" t="n">
-        <v>3.31</v>
+        <v>3.12</v>
       </c>
       <c r="O14" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="P14" t="n">
         <v>1.95</v>
@@ -2250,13 +2250,13 @@
         <v>1.08</v>
       </c>
       <c r="W14" t="n">
-        <v>1.44</v>
+        <v>1.52</v>
       </c>
       <c r="X14" t="n">
-        <v>2.63</v>
+        <v>2.35</v>
       </c>
       <c r="Y14" t="n">
-        <v>2.51</v>
+        <v>2.5</v>
       </c>
       <c r="Z14" t="n">
         <v>1.53</v>
@@ -2268,7 +2268,7 @@
         <v>1.17</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.03</v>
+        <v>1.95</v>
       </c>
       <c r="AD14" t="n">
         <v>1.75</v>
@@ -2346,13 +2346,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.1</v>
+        <v>1.99</v>
       </c>
       <c r="M15" t="n">
-        <v>3</v>
+        <v>3.11</v>
       </c>
       <c r="N15" t="n">
-        <v>3.52</v>
+        <v>3.39</v>
       </c>
       <c r="O15" t="n">
         <v>2.63</v>
@@ -2385,13 +2385,13 @@
         <v>3</v>
       </c>
       <c r="Y15" t="n">
-        <v>2.05</v>
+        <v>2.12</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AA15" t="n">
-        <v>3.54</v>
+        <v>3.75</v>
       </c>
       <c r="AB15" t="n">
         <v>1.25</v>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,61 +2475,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.91</v>
+        <v>2.14</v>
       </c>
       <c r="M16" t="n">
-        <v>3.12</v>
+        <v>3.14</v>
       </c>
       <c r="N16" t="n">
-        <v>2.53</v>
+        <v>2.99</v>
       </c>
       <c r="O16" t="n">
-        <v>3.25</v>
+        <v>2.86</v>
       </c>
       <c r="P16" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.4</v>
+        <v>3.84</v>
       </c>
       <c r="R16" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="S16" t="n">
-        <v>2.5</v>
+        <v>2.65</v>
       </c>
       <c r="T16" t="n">
-        <v>3.3</v>
+        <v>2.94</v>
       </c>
       <c r="U16" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="V16" t="n">
-        <v>1.1</v>
+        <v>1.02</v>
       </c>
       <c r="W16" t="n">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="X16" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="Y16" t="n">
-        <v>2.4</v>
+        <v>1.98</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.5</v>
+        <v>1.73</v>
       </c>
       <c r="AA16" t="n">
-        <v>4.8</v>
+        <v>3.54</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AC16" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.75</v>
+        <v>1.9</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.4</v>
+        <v>1.63</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,61 +2604,61 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.14</v>
+        <v>2.11</v>
       </c>
       <c r="M17" t="n">
-        <v>3.14</v>
+        <v>2.87</v>
       </c>
       <c r="N17" t="n">
-        <v>2.99</v>
+        <v>3.36</v>
       </c>
       <c r="O17" t="n">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="P17" t="n">
-        <v>2.02</v>
+        <v>1.88</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.84</v>
+        <v>4.4</v>
       </c>
       <c r="R17" t="n">
-        <v>1.42</v>
+        <v>1.56</v>
       </c>
       <c r="S17" t="n">
-        <v>2.65</v>
+        <v>2.34</v>
       </c>
       <c r="T17" t="n">
-        <v>2.94</v>
+        <v>3.58</v>
       </c>
       <c r="U17" t="n">
-        <v>1.35</v>
+        <v>1.23</v>
       </c>
       <c r="V17" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="W17" t="n">
-        <v>1.31</v>
+        <v>1.55</v>
       </c>
       <c r="X17" t="n">
-        <v>2.94</v>
+        <v>2.5</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.12</v>
+        <v>2.4</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="AA17" t="n">
-        <v>3.54</v>
+        <v>4.9</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.22</v>
+        <v>1.11</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.8</v>
+        <v>2.17</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.95</v>
+        <v>1.64</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,61 +2733,61 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.2</v>
+        <v>2.47</v>
       </c>
       <c r="M18" t="n">
-        <v>3.1</v>
+        <v>2.93</v>
       </c>
       <c r="N18" t="n">
-        <v>3.5</v>
+        <v>2.68</v>
       </c>
       <c r="O18" t="n">
-        <v>2.9</v>
+        <v>3.25</v>
       </c>
       <c r="P18" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.4</v>
+        <v>3.4</v>
       </c>
       <c r="R18" t="n">
-        <v>1.56</v>
+        <v>1.44</v>
       </c>
       <c r="S18" t="n">
-        <v>2.34</v>
+        <v>2.5</v>
       </c>
       <c r="T18" t="n">
-        <v>3.58</v>
+        <v>3.3</v>
       </c>
       <c r="U18" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="V18" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="W18" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X18" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Z18" t="n">
         <v>1.55</v>
       </c>
-      <c r="X18" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>1.43</v>
-      </c>
       <c r="AA18" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.23</v>
+        <v>2</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.67</v>
+        <v>1.4</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
@@ -2862,16 +2862,16 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="M19" t="n">
-        <v>3.58</v>
+        <v>3.6</v>
       </c>
       <c r="N19" t="n">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="O19" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="P19" t="n">
         <v>2.1</v>
@@ -2901,16 +2901,16 @@
         <v>3.28</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AA19" t="n">
         <v>3.14</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="AC19" t="n">
         <v>1.69</v>

--- a/jogos_2025-10-15.xlsx
+++ b/jogos_2025-10-15.xlsx
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Homeboyz</t>
+          <t>Murang'a SEAL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bidco United</t>
+          <t>Sofapaka</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Murang'a SEAL</t>
+          <t>Homeboyz</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sofapaka</t>
+          <t>Bidco United</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>Leopards</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ibri</t>
+          <t>Bandari</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Leopards</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bandari</t>
+          <t>Ibri</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1572,13 +1572,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1611,10 +1611,10 @@
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AA9" t="n">
         <v>0</v>
@@ -1971,31 +1971,31 @@
         <v>1.83</v>
       </c>
       <c r="P12" t="n">
-        <v>2.38</v>
+        <v>2.54</v>
       </c>
       <c r="Q12" t="n">
-        <v>7.2</v>
+        <v>8.49</v>
       </c>
       <c r="R12" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="S12" t="n">
-        <v>3.04</v>
+        <v>3.2</v>
       </c>
       <c r="T12" t="n">
-        <v>2.59</v>
+        <v>2.75</v>
       </c>
       <c r="U12" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="V12" t="n">
         <v>1.01</v>
       </c>
       <c r="W12" t="n">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="X12" t="n">
-        <v>3.54</v>
+        <v>3.77</v>
       </c>
       <c r="Y12" t="n">
         <v>1.78</v>
@@ -2004,13 +2004,13 @@
         <v>1.92</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.85</v>
+        <v>3.11</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.06</v>
+        <v>2.18</v>
       </c>
       <c r="AD12" t="n">
         <v>1.68</v>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AH12" t="n">
-        <v>3.02</v>
+        <v>3.36</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2097,13 +2097,13 @@
         <v>1.97</v>
       </c>
       <c r="O13" t="n">
-        <v>4.4</v>
+        <v>3.88</v>
       </c>
       <c r="P13" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.74</v>
+        <v>2.6</v>
       </c>
       <c r="R13" t="n">
         <v>1.47</v>
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AI13" t="n">
         <v>0</v>
@@ -2226,13 +2226,13 @@
         <v>3.12</v>
       </c>
       <c r="O14" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="P14" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.75</v>
+        <v>3.59</v>
       </c>
       <c r="R14" t="n">
         <v>1.44</v>
@@ -2268,10 +2268,10 @@
         <v>1.17</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.95</v>
+        <v>2.04</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.57</v>
+        <v>1.63</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2355,13 +2355,13 @@
         <v>3.39</v>
       </c>
       <c r="O15" t="n">
-        <v>2.63</v>
+        <v>2.59</v>
       </c>
       <c r="P15" t="n">
-        <v>2.1</v>
+        <v>2.01</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.9</v>
+        <v>3.74</v>
       </c>
       <c r="R15" t="n">
         <v>1.4</v>
@@ -2397,10 +2397,10 @@
         <v>1.25</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2416,7 +2416,7 @@
         <v>1.33</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,61 +2475,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.14</v>
+        <v>2.47</v>
       </c>
       <c r="M16" t="n">
-        <v>3.14</v>
+        <v>2.93</v>
       </c>
       <c r="N16" t="n">
-        <v>2.99</v>
+        <v>2.68</v>
       </c>
       <c r="O16" t="n">
-        <v>2.86</v>
+        <v>3.25</v>
       </c>
       <c r="P16" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.84</v>
+        <v>3.4</v>
       </c>
       <c r="R16" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="S16" t="n">
-        <v>2.65</v>
+        <v>2.5</v>
       </c>
       <c r="T16" t="n">
-        <v>2.94</v>
+        <v>3.3</v>
       </c>
       <c r="U16" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="V16" t="n">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="W16" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="X16" t="n">
         <v>2.45</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.98</v>
+        <v>2.45</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.73</v>
+        <v>1.55</v>
       </c>
       <c r="AA16" t="n">
-        <v>3.54</v>
+        <v>4.8</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.8</v>
+        <v>2.13</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.9</v>
+        <v>1.72</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.63</v>
+        <v>1.41</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2613,13 +2613,13 @@
         <v>3.36</v>
       </c>
       <c r="O17" t="n">
-        <v>2.9</v>
+        <v>2.73</v>
       </c>
       <c r="P17" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.4</v>
+        <v>4.11</v>
       </c>
       <c r="R17" t="n">
         <v>1.56</v>
@@ -2655,10 +2655,10 @@
         <v>1.11</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.17</v>
+        <v>2.13</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,61 +2733,61 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.47</v>
+        <v>2.14</v>
       </c>
       <c r="M18" t="n">
-        <v>2.93</v>
+        <v>3.14</v>
       </c>
       <c r="N18" t="n">
-        <v>2.68</v>
+        <v>2.99</v>
       </c>
       <c r="O18" t="n">
-        <v>3.25</v>
+        <v>2.86</v>
       </c>
       <c r="P18" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.4</v>
+        <v>3.84</v>
       </c>
       <c r="R18" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="S18" t="n">
-        <v>2.5</v>
+        <v>2.65</v>
       </c>
       <c r="T18" t="n">
-        <v>3.3</v>
+        <v>2.94</v>
       </c>
       <c r="U18" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="V18" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="W18" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="X18" t="n">
         <v>2.45</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.45</v>
+        <v>1.98</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.55</v>
+        <v>1.73</v>
       </c>
       <c r="AA18" t="n">
-        <v>4.8</v>
+        <v>3.54</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AC18" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.75</v>
+        <v>1.92</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.4</v>
+        <v>1.64</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
@@ -2871,34 +2871,34 @@
         <v>2.55</v>
       </c>
       <c r="O19" t="n">
-        <v>2.94</v>
+        <v>2.95</v>
       </c>
       <c r="P19" t="n">
         <v>2.1</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.46</v>
+        <v>3.3</v>
       </c>
       <c r="R19" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="S19" t="n">
-        <v>2.86</v>
+        <v>2.8</v>
       </c>
       <c r="T19" t="n">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="U19" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="V19" t="n">
         <v>1.01</v>
       </c>
       <c r="W19" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="X19" t="n">
-        <v>3.28</v>
+        <v>3.4</v>
       </c>
       <c r="Y19" t="n">
         <v>1.9</v>
@@ -2907,16 +2907,16 @@
         <v>1.8</v>
       </c>
       <c r="AA19" t="n">
-        <v>3.14</v>
+        <v>3.25</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="AD19" t="n">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2929,10 +2929,10 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>

--- a/jogos_2025-10-15.xlsx
+++ b/jogos_2025-10-15.xlsx
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Murang'a SEAL</t>
+          <t>Homeboyz</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sofapaka</t>
+          <t>Bidco United</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Homeboyz</t>
+          <t>Murang'a SEAL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bidco United</t>
+          <t>Sofapaka</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,61 +2217,61 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.24</v>
+        <v>1.99</v>
       </c>
       <c r="M14" t="n">
-        <v>2.84</v>
+        <v>3.11</v>
       </c>
       <c r="N14" t="n">
-        <v>3.12</v>
+        <v>3.39</v>
       </c>
       <c r="O14" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T14" t="n">
         <v>2.9</v>
       </c>
-      <c r="P14" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>3.59</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T14" t="n">
-        <v>3.3</v>
-      </c>
       <c r="U14" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="V14" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="W14" t="n">
-        <v>1.52</v>
+        <v>1.33</v>
       </c>
       <c r="X14" t="n">
-        <v>2.35</v>
+        <v>3</v>
       </c>
       <c r="Y14" t="n">
-        <v>2.5</v>
+        <v>2.12</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.53</v>
+        <v>1.72</v>
       </c>
       <c r="AA14" t="n">
-        <v>4.6</v>
+        <v>3.75</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.04</v>
+        <v>1.86</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.78</v>
+        <v>1.94</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.63</v>
+        <v>1.75</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,61 +2346,61 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.99</v>
+        <v>2.24</v>
       </c>
       <c r="M15" t="n">
-        <v>3.11</v>
+        <v>2.84</v>
       </c>
       <c r="N15" t="n">
-        <v>3.39</v>
+        <v>3.12</v>
       </c>
       <c r="O15" t="n">
-        <v>2.59</v>
+        <v>2.9</v>
       </c>
       <c r="P15" t="n">
-        <v>2.01</v>
+        <v>1.9</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.74</v>
+        <v>3.59</v>
       </c>
       <c r="R15" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="S15" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="T15" t="n">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="U15" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="V15" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="W15" t="n">
-        <v>1.33</v>
+        <v>1.52</v>
       </c>
       <c r="X15" t="n">
-        <v>3</v>
+        <v>2.35</v>
       </c>
       <c r="Y15" t="n">
-        <v>2.12</v>
+        <v>2.5</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.72</v>
+        <v>1.53</v>
       </c>
       <c r="AA15" t="n">
-        <v>3.75</v>
+        <v>4.6</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.86</v>
+        <v>2.04</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.94</v>
+        <v>1.78</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.75</v>
+        <v>1.63</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,61 +2475,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.47</v>
+        <v>2.14</v>
       </c>
       <c r="M16" t="n">
-        <v>2.93</v>
+        <v>3.14</v>
       </c>
       <c r="N16" t="n">
-        <v>2.68</v>
+        <v>2.99</v>
       </c>
       <c r="O16" t="n">
-        <v>3.25</v>
+        <v>2.86</v>
       </c>
       <c r="P16" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.4</v>
+        <v>3.84</v>
       </c>
       <c r="R16" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="S16" t="n">
-        <v>2.5</v>
+        <v>2.65</v>
       </c>
       <c r="T16" t="n">
-        <v>3.3</v>
+        <v>2.94</v>
       </c>
       <c r="U16" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="V16" t="n">
-        <v>1.1</v>
+        <v>1.02</v>
       </c>
       <c r="W16" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="X16" t="n">
         <v>2.45</v>
       </c>
       <c r="Y16" t="n">
-        <v>2.45</v>
+        <v>1.98</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.55</v>
+        <v>1.73</v>
       </c>
       <c r="AA16" t="n">
-        <v>4.8</v>
+        <v>3.54</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.13</v>
+        <v>1.88</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.72</v>
+        <v>1.92</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.41</v>
+        <v>1.64</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,61 +2733,61 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.14</v>
+        <v>2.47</v>
       </c>
       <c r="M18" t="n">
-        <v>3.14</v>
+        <v>2.93</v>
       </c>
       <c r="N18" t="n">
-        <v>2.99</v>
+        <v>2.68</v>
       </c>
       <c r="O18" t="n">
-        <v>2.86</v>
+        <v>3.25</v>
       </c>
       <c r="P18" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.84</v>
+        <v>3.4</v>
       </c>
       <c r="R18" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="S18" t="n">
-        <v>2.65</v>
+        <v>2.5</v>
       </c>
       <c r="T18" t="n">
-        <v>2.94</v>
+        <v>3.3</v>
       </c>
       <c r="U18" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="V18" t="n">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="W18" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="X18" t="n">
         <v>2.45</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.98</v>
+        <v>2.45</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.73</v>
+        <v>1.55</v>
       </c>
       <c r="AA18" t="n">
-        <v>3.54</v>
+        <v>4.8</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.88</v>
+        <v>2.13</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.92</v>
+        <v>1.72</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.64</v>
+        <v>1.41</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>

--- a/jogos_2025-10-15.xlsx
+++ b/jogos_2025-10-15.xlsx
@@ -669,13 +669,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -708,10 +708,10 @@
         <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AA2" t="n">
         <v>0</v>
@@ -757,7 +757,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -798,61 +798,61 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>5.94</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -877,7 +877,7 @@
         <v>0</v>
       </c>
       <c r="AK3" s="3" t="n">
-        <v>45945.375</v>
+        <v>45945.33333333334</v>
       </c>
     </row>
     <row r="4">
@@ -927,13 +927,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -966,10 +966,10 @@
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AA4" t="n">
         <v>0</v>
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Leopards</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bandari</t>
+          <t>Ibri</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,13 +1056,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1095,10 +1095,10 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AA5" t="n">
         <v>0</v>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>Leopards</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ibri</t>
+          <t>Bandari</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,13 +1185,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1224,10 +1224,10 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AA6" t="n">
         <v>0</v>
@@ -1968,34 +1968,34 @@
         <v>7.2</v>
       </c>
       <c r="O12" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="P12" t="n">
-        <v>2.54</v>
+        <v>2.26</v>
       </c>
       <c r="Q12" t="n">
-        <v>8.49</v>
+        <v>6.09</v>
       </c>
       <c r="R12" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="S12" t="n">
-        <v>3.2</v>
+        <v>3.04</v>
       </c>
       <c r="T12" t="n">
-        <v>2.75</v>
+        <v>2.57</v>
       </c>
       <c r="U12" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="V12" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="W12" t="n">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="X12" t="n">
-        <v>3.77</v>
+        <v>3.54</v>
       </c>
       <c r="Y12" t="n">
         <v>1.78</v>
@@ -2004,16 +2004,16 @@
         <v>1.92</v>
       </c>
       <c r="AA12" t="n">
-        <v>3.11</v>
+        <v>2.85</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         <v>1.18</v>
       </c>
       <c r="AH12" t="n">
-        <v>3.36</v>
+        <v>3.3</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2106,16 +2106,16 @@
         <v>2.6</v>
       </c>
       <c r="R13" t="n">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="S13" t="n">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="T13" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="U13" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="V13" t="n">
         <v>1.03</v>
@@ -2133,16 +2133,16 @@
         <v>1.65</v>
       </c>
       <c r="AA13" t="n">
-        <v>3.94</v>
+        <v>3.96</v>
       </c>
       <c r="AB13" t="n">
         <v>1.18</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="AH13" t="n">
         <v>1.27</v>
@@ -2268,10 +2268,10 @@
         <v>1.25</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2287,7 +2287,7 @@
         <v>1.33</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,61 +2475,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.14</v>
+        <v>2.47</v>
       </c>
       <c r="M16" t="n">
-        <v>3.14</v>
+        <v>2.93</v>
       </c>
       <c r="N16" t="n">
-        <v>2.99</v>
+        <v>2.68</v>
       </c>
       <c r="O16" t="n">
-        <v>2.86</v>
+        <v>3.5</v>
       </c>
       <c r="P16" t="n">
-        <v>2.02</v>
+        <v>1.95</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.84</v>
+        <v>3.1</v>
       </c>
       <c r="R16" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="S16" t="n">
-        <v>2.65</v>
+        <v>2.5</v>
       </c>
       <c r="T16" t="n">
-        <v>2.94</v>
+        <v>3.3</v>
       </c>
       <c r="U16" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="V16" t="n">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="W16" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="X16" t="n">
         <v>2.45</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.98</v>
+        <v>2.45</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.73</v>
+        <v>1.55</v>
       </c>
       <c r="AA16" t="n">
-        <v>3.54</v>
+        <v>4.8</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.88</v>
+        <v>2.13</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.92</v>
+        <v>1.72</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.64</v>
+        <v>1.41</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2613,13 +2613,13 @@
         <v>3.36</v>
       </c>
       <c r="O17" t="n">
-        <v>2.73</v>
+        <v>2.9</v>
       </c>
       <c r="P17" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.11</v>
+        <v>4.4</v>
       </c>
       <c r="R17" t="n">
         <v>1.56</v>
@@ -2658,7 +2658,7 @@
         <v>2.13</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,61 +2733,61 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.47</v>
+        <v>2.14</v>
       </c>
       <c r="M18" t="n">
-        <v>2.93</v>
+        <v>3.14</v>
       </c>
       <c r="N18" t="n">
-        <v>2.68</v>
+        <v>2.99</v>
       </c>
       <c r="O18" t="n">
-        <v>3.25</v>
+        <v>2.86</v>
       </c>
       <c r="P18" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.4</v>
+        <v>3.84</v>
       </c>
       <c r="R18" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="S18" t="n">
-        <v>2.5</v>
+        <v>2.65</v>
       </c>
       <c r="T18" t="n">
-        <v>3.3</v>
+        <v>2.94</v>
       </c>
       <c r="U18" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="V18" t="n">
-        <v>1.1</v>
+        <v>1.02</v>
       </c>
       <c r="W18" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="X18" t="n">
         <v>2.45</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.45</v>
+        <v>1.98</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.55</v>
+        <v>1.73</v>
       </c>
       <c r="AA18" t="n">
-        <v>4.8</v>
+        <v>3.54</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.13</v>
+        <v>1.88</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.72</v>
+        <v>1.92</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.41</v>
+        <v>1.64</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
@@ -2871,13 +2871,13 @@
         <v>2.55</v>
       </c>
       <c r="O19" t="n">
-        <v>2.95</v>
+        <v>2.88</v>
       </c>
       <c r="P19" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="R19" t="n">
         <v>1.38</v>
@@ -2907,10 +2907,10 @@
         <v>1.8</v>
       </c>
       <c r="AA19" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AC19" t="n">
         <v>1.67</v>
@@ -2932,7 +2932,7 @@
         <v>1.25</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>

--- a/jogos_2025-10-15.xlsx
+++ b/jogos_2025-10-15.xlsx
@@ -669,61 +669,61 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.81</v>
+        <v>1.75</v>
       </c>
       <c r="M2" t="n">
-        <v>3.04</v>
+        <v>3</v>
       </c>
       <c r="N2" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="Y2" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AK2" s="3" t="n">
         <v>45945.33333333334</v>
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.72</v>
+        <v>1.65</v>
       </c>
       <c r="M3" t="n">
-        <v>3.07</v>
+        <v>3</v>
       </c>
       <c r="N3" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="O3" t="n">
         <v>2.44</v>
@@ -837,10 +837,10 @@
         <v>2.7</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.52</v>
+        <v>1.58</v>
       </c>
       <c r="AA3" t="n">
         <v>4.1</v>
@@ -871,10 +871,10 @@
         <v>1.9</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="AK3" s="3" t="n">
         <v>45945.33333333334</v>
@@ -927,61 +927,61 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="M4" t="n">
+        <v>3</v>
+      </c>
+      <c r="N4" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="O4" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="P4" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S4" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="T4" t="n">
         <v>3.05</v>
       </c>
-      <c r="N4" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T4" t="n">
-        <v>0</v>
-      </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -994,16 +994,16 @@
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AK4" s="3" t="n">
         <v>45945.375</v>
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>Leopards</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ibri</t>
+          <t>Bandari</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,62 +1056,62 @@
         </is>
       </c>
       <c r="L5" t="n">
+        <v>2</v>
+      </c>
+      <c r="M5" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="N5" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="O5" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X5" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AD5" t="n">
         <v>1.68</v>
       </c>
-      <c r="M5" t="n">
-        <v>3.47</v>
-      </c>
-      <c r="N5" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>0</v>
-      </c>
       <c r="AE5" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1123,16 +1123,16 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AK5" s="3" t="n">
         <v>45945.41666666666</v>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Leopards</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bandari</t>
+          <t>Ibri</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,83 +1185,83 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.02</v>
+        <v>1.52</v>
       </c>
       <c r="M6" t="n">
-        <v>2.94</v>
+        <v>3.49</v>
       </c>
       <c r="N6" t="n">
-        <v>3.76</v>
+        <v>5.91</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.35</v>
+        <v>2.24</v>
       </c>
       <c r="Z6" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG6" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AI6" t="n">
         <v>1.53</v>
       </c>
-      <c r="AA6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>0</v>
-      </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AK6" s="3" t="n">
         <v>45945.41666666666</v>
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,61 +2217,61 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.99</v>
+        <v>2.24</v>
       </c>
       <c r="M14" t="n">
-        <v>3.11</v>
+        <v>2.84</v>
       </c>
       <c r="N14" t="n">
-        <v>3.39</v>
+        <v>3.12</v>
       </c>
       <c r="O14" t="n">
-        <v>2.59</v>
+        <v>2.9</v>
       </c>
       <c r="P14" t="n">
-        <v>2.01</v>
+        <v>1.9</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.74</v>
+        <v>3.59</v>
       </c>
       <c r="R14" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="S14" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="T14" t="n">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="U14" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="V14" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="W14" t="n">
-        <v>1.33</v>
+        <v>1.52</v>
       </c>
       <c r="X14" t="n">
-        <v>3</v>
+        <v>2.35</v>
       </c>
       <c r="Y14" t="n">
-        <v>2.12</v>
+        <v>2.5</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.72</v>
+        <v>1.53</v>
       </c>
       <c r="AA14" t="n">
-        <v>3.75</v>
+        <v>4.6</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.88</v>
+        <v>2.04</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.92</v>
+        <v>1.78</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.79</v>
+        <v>1.61</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,61 +2346,61 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.24</v>
+        <v>1.99</v>
       </c>
       <c r="M15" t="n">
-        <v>2.84</v>
+        <v>3.11</v>
       </c>
       <c r="N15" t="n">
-        <v>3.12</v>
+        <v>3.39</v>
       </c>
       <c r="O15" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T15" t="n">
         <v>2.9</v>
       </c>
-      <c r="P15" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>3.59</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T15" t="n">
-        <v>3.3</v>
-      </c>
       <c r="U15" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="V15" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="W15" t="n">
-        <v>1.52</v>
+        <v>1.33</v>
       </c>
       <c r="X15" t="n">
-        <v>2.35</v>
+        <v>3</v>
       </c>
       <c r="Y15" t="n">
-        <v>2.5</v>
+        <v>2.12</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.53</v>
+        <v>1.72</v>
       </c>
       <c r="AA15" t="n">
-        <v>4.6</v>
+        <v>3.75</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.04</v>
+        <v>1.88</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.78</v>
+        <v>1.92</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.61</v>
+        <v>1.79</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,61 +2475,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.47</v>
+        <v>2.11</v>
       </c>
       <c r="M16" t="n">
-        <v>2.93</v>
+        <v>2.87</v>
       </c>
       <c r="N16" t="n">
-        <v>2.68</v>
+        <v>3.36</v>
       </c>
       <c r="O16" t="n">
-        <v>3.5</v>
+        <v>2.9</v>
       </c>
       <c r="P16" t="n">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.1</v>
+        <v>4.4</v>
       </c>
       <c r="R16" t="n">
-        <v>1.44</v>
+        <v>1.56</v>
       </c>
       <c r="S16" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="T16" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="X16" t="n">
         <v>2.5</v>
       </c>
-      <c r="T16" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="W16" t="n">
+      <c r="Y16" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Z16" t="n">
         <v>1.5</v>
       </c>
-      <c r="X16" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>1.55</v>
-      </c>
       <c r="AA16" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="AC16" t="n">
         <v>2.13</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.72</v>
+        <v>1.64</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.41</v>
+        <v>1.67</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,77 +2604,77 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.11</v>
+        <v>2.14</v>
       </c>
       <c r="M17" t="n">
-        <v>2.87</v>
+        <v>3.14</v>
       </c>
       <c r="N17" t="n">
-        <v>3.36</v>
+        <v>2.99</v>
       </c>
       <c r="O17" t="n">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="P17" t="n">
-        <v>1.88</v>
+        <v>2.02</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.4</v>
+        <v>3.84</v>
       </c>
       <c r="R17" t="n">
-        <v>1.56</v>
+        <v>1.42</v>
       </c>
       <c r="S17" t="n">
-        <v>2.34</v>
+        <v>2.65</v>
       </c>
       <c r="T17" t="n">
-        <v>3.58</v>
+        <v>2.94</v>
       </c>
       <c r="U17" t="n">
-        <v>1.23</v>
+        <v>1.35</v>
       </c>
       <c r="V17" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="W17" t="n">
         <v>1.55</v>
       </c>
       <c r="X17" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.4</v>
+        <v>1.98</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.5</v>
+        <v>1.73</v>
       </c>
       <c r="AA17" t="n">
-        <v>4.9</v>
+        <v>3.54</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.11</v>
+        <v>1.22</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.13</v>
+        <v>1.88</v>
       </c>
       <c r="AD17" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG17" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AH17" t="n">
         <v>1.64</v>
-      </c>
-      <c r="AE17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG17" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>1.67</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,61 +2733,61 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.14</v>
+        <v>2.47</v>
       </c>
       <c r="M18" t="n">
-        <v>3.14</v>
+        <v>2.93</v>
       </c>
       <c r="N18" t="n">
-        <v>2.99</v>
+        <v>2.68</v>
       </c>
       <c r="O18" t="n">
-        <v>2.86</v>
+        <v>3.5</v>
       </c>
       <c r="P18" t="n">
-        <v>2.02</v>
+        <v>1.95</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.84</v>
+        <v>3.1</v>
       </c>
       <c r="R18" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="S18" t="n">
-        <v>2.65</v>
+        <v>2.5</v>
       </c>
       <c r="T18" t="n">
-        <v>2.94</v>
+        <v>3.3</v>
       </c>
       <c r="U18" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="V18" t="n">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="W18" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="X18" t="n">
         <v>2.45</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.98</v>
+        <v>2.45</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.73</v>
+        <v>1.55</v>
       </c>
       <c r="AA18" t="n">
-        <v>3.54</v>
+        <v>4.8</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.88</v>
+        <v>2.13</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.92</v>
+        <v>1.72</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.64</v>
+        <v>1.41</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>

--- a/jogos_2025-10-15.xlsx
+++ b/jogos_2025-10-15.xlsx
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Shabana</t>
+          <t>Homeboyz</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Posta Rangers</t>
+          <t>Bidco United</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -669,61 +669,61 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="M2" t="n">
-        <v>3</v>
+        <v>3.07</v>
       </c>
       <c r="N2" t="n">
-        <v>4.4</v>
+        <v>5.1</v>
       </c>
       <c r="O2" t="n">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="P2" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="Q2" t="n">
-        <v>5.3</v>
+        <v>5.94</v>
       </c>
       <c r="R2" t="n">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="S2" t="n">
-        <v>2.51</v>
+        <v>2.38</v>
       </c>
       <c r="T2" t="n">
-        <v>2.9</v>
+        <v>3.22</v>
       </c>
       <c r="U2" t="n">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="V2" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="W2" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="X2" t="n">
-        <v>3.08</v>
+        <v>2.7</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.99</v>
+        <v>2.3</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.73</v>
+        <v>1.55</v>
       </c>
       <c r="AA2" t="n">
-        <v>3.28</v>
+        <v>4.1</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.83</v>
+        <v>2.05</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.86</v>
+        <v>1.67</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.84</v>
+        <v>1.9</v>
       </c>
       <c r="AI2" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="AJ2" t="n">
-        <v>2.81</v>
+        <v>2.99</v>
       </c>
       <c r="AK2" s="3" t="n">
         <v>45945.33333333334</v>
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Homeboyz</t>
+          <t>Shabana</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bidco United</t>
+          <t>Posta Rangers</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,83 +798,83 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.65</v>
+        <v>1.81</v>
       </c>
       <c r="M3" t="n">
-        <v>3</v>
+        <v>3.04</v>
       </c>
       <c r="N3" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="O3" t="n">
-        <v>2.44</v>
+        <v>2.47</v>
       </c>
       <c r="P3" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="Q3" t="n">
-        <v>5.94</v>
+        <v>5.56</v>
       </c>
       <c r="R3" t="n">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="S3" t="n">
-        <v>2.38</v>
+        <v>2.51</v>
       </c>
       <c r="T3" t="n">
-        <v>3.22</v>
+        <v>2.9</v>
       </c>
       <c r="U3" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W3" t="n">
         <v>1.28</v>
       </c>
-      <c r="V3" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.36</v>
-      </c>
       <c r="X3" t="n">
-        <v>2.7</v>
+        <v>3.08</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.24</v>
+        <v>2</v>
       </c>
       <c r="Z3" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG3" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AI3" t="n">
         <v>1.58</v>
       </c>
-      <c r="AA3" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG3" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>1.56</v>
-      </c>
       <c r="AJ3" t="n">
-        <v>2.99</v>
+        <v>2.81</v>
       </c>
       <c r="AK3" s="3" t="n">
         <v>45945.33333333334</v>
@@ -927,13 +927,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="M4" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="N4" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="O4" t="n">
         <v>3.2</v>
@@ -966,10 +966,10 @@
         <v>2.7</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AA4" t="n">
         <v>3.85</v>
@@ -1056,22 +1056,22 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="M5" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="N5" t="n">
-        <v>3.7</v>
+        <v>3.76</v>
       </c>
       <c r="O5" t="n">
-        <v>2.69</v>
+        <v>2.71</v>
       </c>
       <c r="P5" t="n">
         <v>1.94</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.33</v>
+        <v>4.52</v>
       </c>
       <c r="R5" t="n">
         <v>1.47</v>
@@ -1095,7 +1095,7 @@
         <v>2.56</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.34</v>
+        <v>2.35</v>
       </c>
       <c r="Z5" t="n">
         <v>1.53</v>
@@ -1185,28 +1185,28 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.52</v>
+        <v>1.68</v>
       </c>
       <c r="M6" t="n">
-        <v>3.49</v>
+        <v>3.47</v>
       </c>
       <c r="N6" t="n">
-        <v>5.91</v>
+        <v>4.6</v>
       </c>
       <c r="O6" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="P6" t="n">
-        <v>1.99</v>
+        <v>1.94</v>
       </c>
       <c r="Q6" t="n">
-        <v>6.7</v>
+        <v>6.54</v>
       </c>
       <c r="R6" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="S6" t="n">
-        <v>2.46</v>
+        <v>2.41</v>
       </c>
       <c r="T6" t="n">
         <v>3.28</v>
@@ -1215,31 +1215,31 @@
         <v>1.27</v>
       </c>
       <c r="V6" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="W6" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="X6" t="n">
-        <v>2.67</v>
+        <v>2.62</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="AA6" t="n">
-        <v>4.15</v>
+        <v>4.25</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.23</v>
+        <v>2.17</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AH6" t="n">
-        <v>2.25</v>
+        <v>2.07</v>
       </c>
       <c r="AI6" t="n">
         <v>1.53</v>
@@ -1959,83 +1959,83 @@
         </is>
       </c>
       <c r="L12" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="M12" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="N12" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="S12" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="X12" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG12" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AI12" t="n">
         <v>1.36</v>
       </c>
-      <c r="M12" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="N12" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="O12" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="P12" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>6.09</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S12" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="X12" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AE12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG12" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>0</v>
-      </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AK12" s="3" t="n">
         <v>45945.79166666666</v>
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="M13" t="n">
-        <v>2.95</v>
+        <v>3.18</v>
       </c>
       <c r="N13" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="O13" t="n">
         <v>3.88</v>
@@ -2112,13 +2112,13 @@
         <v>2.62</v>
       </c>
       <c r="T13" t="n">
-        <v>3.1</v>
+        <v>3.22</v>
       </c>
       <c r="U13" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="V13" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="W13" t="n">
         <v>1.36</v>
@@ -2127,22 +2127,22 @@
         <v>2.72</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.25</v>
+        <v>2.29</v>
       </c>
       <c r="Z13" t="n">
         <v>1.65</v>
       </c>
       <c r="AA13" t="n">
-        <v>3.96</v>
+        <v>3.98</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AC13" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2158,13 +2158,13 @@
         <v>1.38</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AK13" s="3" t="n">
         <v>45945.8125</v>
@@ -2217,13 +2217,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.24</v>
+        <v>2.42</v>
       </c>
       <c r="M14" t="n">
-        <v>2.84</v>
+        <v>3.1</v>
       </c>
       <c r="N14" t="n">
-        <v>3.12</v>
+        <v>2.91</v>
       </c>
       <c r="O14" t="n">
         <v>2.9</v>
@@ -2232,10 +2232,10 @@
         <v>1.9</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.59</v>
+        <v>3.75</v>
       </c>
       <c r="R14" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="S14" t="n">
         <v>2.5</v>
@@ -2250,13 +2250,13 @@
         <v>1.08</v>
       </c>
       <c r="W14" t="n">
-        <v>1.52</v>
+        <v>1.44</v>
       </c>
       <c r="X14" t="n">
-        <v>2.35</v>
+        <v>2.63</v>
       </c>
       <c r="Y14" t="n">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="Z14" t="n">
         <v>1.53</v>
@@ -2268,7 +2268,7 @@
         <v>1.17</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="AD14" t="n">
         <v>1.78</v>
@@ -2284,16 +2284,16 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AK14" s="3" t="n">
         <v>45945.83333333334</v>
@@ -2346,13 +2346,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="M15" t="n">
-        <v>3.11</v>
+        <v>3</v>
       </c>
       <c r="N15" t="n">
-        <v>3.39</v>
+        <v>3.5</v>
       </c>
       <c r="O15" t="n">
         <v>2.59</v>
@@ -2376,31 +2376,31 @@
         <v>1.36</v>
       </c>
       <c r="V15" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="W15" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="X15" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="Y15" t="n">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="Z15" t="n">
         <v>1.72</v>
       </c>
       <c r="AA15" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.92</v>
+        <v>1.83</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,16 +2413,16 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="AI15" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AK15" s="3" t="n">
         <v>45945.83333333334</v>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,83 +2475,83 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.11</v>
+        <v>2.17</v>
       </c>
       <c r="M16" t="n">
-        <v>2.87</v>
+        <v>3.25</v>
       </c>
       <c r="N16" t="n">
-        <v>3.36</v>
+        <v>2.86</v>
       </c>
       <c r="O16" t="n">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="P16" t="n">
-        <v>1.88</v>
+        <v>2.02</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.4</v>
+        <v>3.84</v>
       </c>
       <c r="R16" t="n">
-        <v>1.56</v>
+        <v>1.42</v>
       </c>
       <c r="S16" t="n">
-        <v>2.34</v>
+        <v>2.65</v>
       </c>
       <c r="T16" t="n">
-        <v>3.58</v>
+        <v>2.94</v>
       </c>
       <c r="U16" t="n">
-        <v>1.23</v>
+        <v>1.35</v>
       </c>
       <c r="V16" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="W16" t="n">
-        <v>1.55</v>
+        <v>1.3</v>
       </c>
       <c r="X16" t="n">
-        <v>2.5</v>
+        <v>2.99</v>
       </c>
       <c r="Y16" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.5</v>
+        <v>1.68</v>
       </c>
       <c r="AA16" t="n">
-        <v>4.9</v>
+        <v>3.85</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.11</v>
+        <v>1.22</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.13</v>
+        <v>1.8</v>
       </c>
       <c r="AD16" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG16" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AH16" t="n">
         <v>1.64</v>
       </c>
-      <c r="AE16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG16" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>1.67</v>
-      </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AK16" s="3" t="n">
         <v>45945.89583333334</v>
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,61 +2604,61 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.14</v>
+        <v>2.9</v>
       </c>
       <c r="M17" t="n">
-        <v>3.14</v>
+        <v>3.1</v>
       </c>
       <c r="N17" t="n">
-        <v>2.99</v>
+        <v>2.5</v>
       </c>
       <c r="O17" t="n">
-        <v>2.86</v>
+        <v>3.5</v>
       </c>
       <c r="P17" t="n">
-        <v>2.02</v>
+        <v>1.89</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.84</v>
+        <v>3.1</v>
       </c>
       <c r="R17" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="S17" t="n">
-        <v>2.65</v>
+        <v>2.5</v>
       </c>
       <c r="T17" t="n">
-        <v>2.94</v>
+        <v>3.3</v>
       </c>
       <c r="U17" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="V17" t="n">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="W17" t="n">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="X17" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.98</v>
+        <v>2.4</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.73</v>
+        <v>1.5</v>
       </c>
       <c r="AA17" t="n">
-        <v>3.54</v>
+        <v>4.8</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.92</v>
+        <v>1.72</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,16 +2671,16 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.64</v>
+        <v>1.41</v>
       </c>
       <c r="AI17" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AK17" s="3" t="n">
         <v>45945.89583333334</v>
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,61 +2733,61 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.47</v>
+        <v>2.1</v>
       </c>
       <c r="M18" t="n">
-        <v>2.93</v>
+        <v>2.8</v>
       </c>
       <c r="N18" t="n">
-        <v>2.68</v>
+        <v>3.5</v>
       </c>
       <c r="O18" t="n">
-        <v>3.5</v>
+        <v>2.9</v>
       </c>
       <c r="P18" t="n">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.1</v>
+        <v>4.4</v>
       </c>
       <c r="R18" t="n">
-        <v>1.44</v>
+        <v>1.56</v>
       </c>
       <c r="S18" t="n">
-        <v>2.5</v>
+        <v>2.34</v>
       </c>
       <c r="T18" t="n">
-        <v>3.3</v>
+        <v>3.58</v>
       </c>
       <c r="U18" t="n">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="V18" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="W18" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="X18" t="n">
-        <v>2.45</v>
+        <v>2.53</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.45</v>
+        <v>2.63</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.55</v>
+        <v>1.43</v>
       </c>
       <c r="AA18" t="n">
-        <v>4.8</v>
+        <v>5.22</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.13</v>
+        <v>2.18</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,16 +2800,16 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.41</v>
+        <v>1.68</v>
       </c>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AK18" s="3" t="n">
         <v>45945.89583333334</v>
@@ -2862,28 +2862,28 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="M19" t="n">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="N19" t="n">
-        <v>2.55</v>
+        <v>3</v>
       </c>
       <c r="O19" t="n">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="P19" t="n">
         <v>2.05</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.45</v>
+        <v>3.65</v>
       </c>
       <c r="R19" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="S19" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="T19" t="n">
         <v>2.75</v>
@@ -2895,28 +2895,28 @@
         <v>1.01</v>
       </c>
       <c r="W19" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="X19" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="Z19" t="n">
         <v>1.8</v>
       </c>
       <c r="AA19" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AD19" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2935,10 +2935,10 @@
         <v>1.62</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AK19" s="3" t="n">
         <v>45945.95833333334</v>

--- a/jogos_2025-10-15.xlsx
+++ b/jogos_2025-10-15.xlsx
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Homeboyz</t>
+          <t>Shabana</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bidco United</t>
+          <t>Posta Rangers</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -669,61 +669,61 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="M2" t="n">
-        <v>3.07</v>
+        <v>3</v>
       </c>
       <c r="N2" t="n">
-        <v>5.1</v>
+        <v>4.55</v>
       </c>
       <c r="O2" t="n">
-        <v>2.44</v>
+        <v>2.53</v>
       </c>
       <c r="P2" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="Q2" t="n">
-        <v>5.94</v>
+        <v>5.52</v>
       </c>
       <c r="R2" t="n">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="S2" t="n">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="T2" t="n">
-        <v>3.22</v>
+        <v>2.94</v>
       </c>
       <c r="U2" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="V2" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="W2" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="X2" t="n">
-        <v>2.7</v>
+        <v>2.97</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.55</v>
+        <v>1.69</v>
       </c>
       <c r="AA2" t="n">
-        <v>4.1</v>
+        <v>3.48</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.05</v>
+        <v>1.87</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.67</v>
+        <v>1.82</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.9</v>
+        <v>1.81</v>
       </c>
       <c r="AI2" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="AJ2" t="n">
-        <v>2.99</v>
+        <v>2.81</v>
       </c>
       <c r="AK2" s="3" t="n">
         <v>45945.33333333334</v>
@@ -757,7 +757,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Shabana</t>
+          <t>Homeboyz</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Posta Rangers</t>
+          <t>Bidco United</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,61 +798,61 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.81</v>
+        <v>1.7</v>
       </c>
       <c r="M3" t="n">
-        <v>3.04</v>
+        <v>3.05</v>
       </c>
       <c r="N3" t="n">
-        <v>4.6</v>
+        <v>5.15</v>
       </c>
       <c r="O3" t="n">
-        <v>2.47</v>
+        <v>2.43</v>
       </c>
       <c r="P3" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="Q3" t="n">
-        <v>5.56</v>
+        <v>5.6</v>
       </c>
       <c r="R3" t="n">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="S3" t="n">
-        <v>2.51</v>
+        <v>2.38</v>
       </c>
       <c r="T3" t="n">
-        <v>2.9</v>
+        <v>3.22</v>
       </c>
       <c r="U3" t="n">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="V3" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="W3" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="X3" t="n">
-        <v>3.08</v>
+        <v>2.7</v>
       </c>
       <c r="Y3" t="n">
-        <v>2</v>
+        <v>2.24</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.72</v>
+        <v>1.58</v>
       </c>
       <c r="AA3" t="n">
-        <v>3.28</v>
+        <v>4.05</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.83</v>
+        <v>2.05</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.86</v>
+        <v>1.67</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -865,19 +865,19 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.84</v>
+        <v>1.9</v>
       </c>
       <c r="AI3" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="AJ3" t="n">
-        <v>2.81</v>
+        <v>2.99</v>
       </c>
       <c r="AK3" s="3" t="n">
-        <v>45945.33333333334</v>
+        <v>45945.375</v>
       </c>
     </row>
     <row r="4">
@@ -927,28 +927,28 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.54</v>
+        <v>2.53</v>
       </c>
       <c r="M4" t="n">
-        <v>3.05</v>
+        <v>2.96</v>
       </c>
       <c r="N4" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="O4" t="n">
-        <v>3.2</v>
+        <v>3.22</v>
       </c>
       <c r="P4" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.38</v>
+        <v>3.44</v>
       </c>
       <c r="R4" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="S4" t="n">
-        <v>2.51</v>
+        <v>2.46</v>
       </c>
       <c r="T4" t="n">
         <v>3.05</v>
@@ -966,22 +966,22 @@
         <v>2.7</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.85</v>
+        <v>3.82</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AH4" t="n">
         <v>1.41</v>
@@ -1056,13 +1056,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.02</v>
+        <v>1.96</v>
       </c>
       <c r="M5" t="n">
-        <v>2.94</v>
+        <v>2.83</v>
       </c>
       <c r="N5" t="n">
-        <v>3.76</v>
+        <v>3.6</v>
       </c>
       <c r="O5" t="n">
         <v>2.71</v>
@@ -1095,7 +1095,7 @@
         <v>2.56</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="Z5" t="n">
         <v>1.53</v>
@@ -1110,7 +1110,7 @@
         <v>2.01</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1959,61 +1959,61 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="M12" t="n">
-        <v>4.8</v>
+        <v>4.1</v>
       </c>
       <c r="N12" t="n">
-        <v>8.199999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="O12" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="P12" t="n">
-        <v>2.56</v>
+        <v>2.39</v>
       </c>
       <c r="Q12" t="n">
-        <v>8.300000000000001</v>
+        <v>7.5</v>
       </c>
       <c r="R12" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="S12" t="n">
-        <v>3.29</v>
+        <v>3.04</v>
       </c>
       <c r="T12" t="n">
-        <v>2.72</v>
+        <v>2.6</v>
       </c>
       <c r="U12" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="V12" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="W12" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="X12" t="n">
-        <v>3.75</v>
+        <v>3.54</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.03</v>
+        <v>1.92</v>
       </c>
       <c r="AA12" t="n">
-        <v>3.16</v>
+        <v>3.05</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.17</v>
+        <v>2.06</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         <v>1.19</v>
       </c>
       <c r="AH12" t="n">
-        <v>3.28</v>
+        <v>3.02</v>
       </c>
       <c r="AI12" t="n">
         <v>1.36</v>
@@ -2088,61 +2088,61 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="M13" t="n">
-        <v>3.18</v>
+        <v>2.95</v>
       </c>
       <c r="N13" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="O13" t="n">
-        <v>3.88</v>
+        <v>4</v>
       </c>
       <c r="P13" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="R13" t="n">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="S13" t="n">
-        <v>2.62</v>
+        <v>2.47</v>
       </c>
       <c r="T13" t="n">
-        <v>3.22</v>
+        <v>3.38</v>
       </c>
       <c r="U13" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="V13" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="W13" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="X13" t="n">
         <v>2.72</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="Z13" t="n">
         <v>1.65</v>
       </c>
       <c r="AA13" t="n">
-        <v>3.98</v>
+        <v>4.2</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.01</v>
+        <v>1.95</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.82</v>
+        <v>1.76</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="AH13" t="n">
         <v>1.26</v>
@@ -2217,31 +2217,31 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.42</v>
+        <v>2.24</v>
       </c>
       <c r="M14" t="n">
-        <v>3.1</v>
+        <v>2.84</v>
       </c>
       <c r="N14" t="n">
-        <v>2.91</v>
+        <v>3.12</v>
       </c>
       <c r="O14" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="P14" t="n">
-        <v>1.9</v>
+        <v>2.03</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="R14" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="S14" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="T14" t="n">
-        <v>3.3</v>
+        <v>3.34</v>
       </c>
       <c r="U14" t="n">
         <v>1.3</v>
@@ -2250,28 +2250,28 @@
         <v>1.08</v>
       </c>
       <c r="W14" t="n">
-        <v>1.44</v>
+        <v>1.52</v>
       </c>
       <c r="X14" t="n">
-        <v>2.63</v>
+        <v>2.35</v>
       </c>
       <c r="Y14" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="Z14" t="n">
         <v>1.53</v>
       </c>
       <c r="AA14" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.06</v>
+        <v>1.95</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AI14" t="n">
         <v>1.83</v>
@@ -2346,61 +2346,61 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="M15" t="n">
-        <v>3</v>
+        <v>3.11</v>
       </c>
       <c r="N15" t="n">
-        <v>3.5</v>
+        <v>3.39</v>
       </c>
       <c r="O15" t="n">
-        <v>2.59</v>
+        <v>2.75</v>
       </c>
       <c r="P15" t="n">
-        <v>2.01</v>
+        <v>2.1</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.74</v>
+        <v>4.1</v>
       </c>
       <c r="R15" t="n">
         <v>1.4</v>
       </c>
       <c r="S15" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="T15" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="U15" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="V15" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="W15" t="n">
         <v>1.36</v>
       </c>
       <c r="X15" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="Y15" t="n">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="Z15" t="n">
         <v>1.72</v>
       </c>
       <c r="AA15" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.87</v>
+        <v>1.92</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.76</v>
+        <v>1.67</v>
       </c>
       <c r="AI15" t="n">
         <v>1.72</v>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,61 +2475,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.17</v>
+        <v>2.47</v>
       </c>
       <c r="M16" t="n">
-        <v>3.25</v>
+        <v>2.93</v>
       </c>
       <c r="N16" t="n">
-        <v>2.86</v>
+        <v>2.68</v>
       </c>
       <c r="O16" t="n">
-        <v>2.86</v>
+        <v>3.5</v>
       </c>
       <c r="P16" t="n">
-        <v>2.02</v>
+        <v>1.97</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.84</v>
+        <v>3.1</v>
       </c>
       <c r="R16" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="S16" t="n">
-        <v>2.65</v>
+        <v>2.5</v>
       </c>
       <c r="T16" t="n">
-        <v>2.94</v>
+        <v>3.3</v>
       </c>
       <c r="U16" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="V16" t="n">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="W16" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="X16" t="n">
-        <v>2.99</v>
+        <v>2.45</v>
       </c>
       <c r="Y16" t="n">
-        <v>2.1</v>
+        <v>2.45</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.68</v>
+        <v>1.55</v>
       </c>
       <c r="AA16" t="n">
-        <v>3.85</v>
+        <v>4.8</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.92</v>
+        <v>1.74</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,16 +2542,16 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.64</v>
+        <v>1.41</v>
       </c>
       <c r="AI16" t="n">
-        <v>1.83</v>
+        <v>2.15</v>
       </c>
       <c r="AJ16" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AK16" s="3" t="n">
         <v>45945.89583333334</v>
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,83 +2604,83 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.9</v>
+        <v>2.14</v>
       </c>
       <c r="M17" t="n">
-        <v>3.1</v>
+        <v>3.14</v>
       </c>
       <c r="N17" t="n">
-        <v>2.5</v>
+        <v>2.99</v>
       </c>
       <c r="O17" t="n">
-        <v>3.5</v>
+        <v>2.85</v>
       </c>
       <c r="P17" t="n">
-        <v>1.89</v>
+        <v>2.17</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.1</v>
+        <v>4.06</v>
       </c>
       <c r="R17" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="S17" t="n">
-        <v>2.5</v>
+        <v>2.65</v>
       </c>
       <c r="T17" t="n">
-        <v>3.3</v>
+        <v>2.95</v>
       </c>
       <c r="U17" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="X17" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>4.01</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG17" t="n">
         <v>1.3</v>
       </c>
-      <c r="V17" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="X17" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AE17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG17" t="n">
-        <v>1.38</v>
-      </c>
       <c r="AH17" t="n">
-        <v>1.41</v>
+        <v>1.63</v>
       </c>
       <c r="AI17" t="n">
-        <v>2.15</v>
+        <v>1.83</v>
       </c>
       <c r="AJ17" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AK17" s="3" t="n">
         <v>45945.89583333334</v>
@@ -2733,61 +2733,61 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="M18" t="n">
-        <v>2.8</v>
+        <v>2.87</v>
       </c>
       <c r="N18" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="O18" t="n">
+        <v>3</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="T18" t="n">
         <v>3.5</v>
-      </c>
-      <c r="O18" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="P18" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="S18" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="T18" t="n">
-        <v>3.58</v>
       </c>
       <c r="U18" t="n">
         <v>1.23</v>
       </c>
       <c r="V18" t="n">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="W18" t="n">
         <v>1.55</v>
       </c>
       <c r="X18" t="n">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.63</v>
+        <v>2.4</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="AA18" t="n">
-        <v>5.22</v>
+        <v>4.9</v>
       </c>
       <c r="AB18" t="n">
         <v>1.11</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.18</v>
+        <v>2.11</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.68</v>
+        <v>1.63</v>
       </c>
       <c r="AI18" t="n">
         <v>1.83</v>
@@ -2862,61 +2862,61 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="M19" t="n">
-        <v>3.25</v>
+        <v>3.32</v>
       </c>
       <c r="N19" t="n">
-        <v>3</v>
+        <v>3.08</v>
       </c>
       <c r="O19" t="n">
         <v>2.8</v>
       </c>
       <c r="P19" t="n">
-        <v>2.05</v>
+        <v>2.11</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.65</v>
+        <v>3.94</v>
       </c>
       <c r="R19" t="n">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="S19" t="n">
-        <v>2.7</v>
+        <v>2.56</v>
       </c>
       <c r="T19" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="U19" t="n">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="V19" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W19" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="X19" t="n">
-        <v>3.2</v>
+        <v>2.84</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="Z19" t="n">
         <v>1.8</v>
       </c>
       <c r="AA19" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.73</v>
+        <v>1.86</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.92</v>
+        <v>1.8</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2929,10 +2929,10 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="AI19" t="n">
         <v>1.8</v>

--- a/jogos_2025-10-15.xlsx
+++ b/jogos_2025-10-15.xlsx
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Shabana</t>
+          <t>Homeboyz</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Posta Rangers</t>
+          <t>Bidco United</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -669,61 +669,61 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="M2" t="n">
-        <v>3</v>
+        <v>3.07</v>
       </c>
       <c r="N2" t="n">
-        <v>4.55</v>
+        <v>5.1</v>
       </c>
       <c r="O2" t="n">
-        <v>2.53</v>
+        <v>2.43</v>
       </c>
       <c r="P2" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="Q2" t="n">
-        <v>5.52</v>
+        <v>5.6</v>
       </c>
       <c r="R2" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="S2" t="n">
-        <v>2.43</v>
+        <v>2.38</v>
       </c>
       <c r="T2" t="n">
-        <v>2.94</v>
+        <v>3.22</v>
       </c>
       <c r="U2" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="V2" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="W2" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="X2" t="n">
-        <v>2.97</v>
+        <v>2.7</v>
       </c>
       <c r="Y2" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AC2" t="n">
         <v>2.05</v>
       </c>
-      <c r="Z2" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>1.87</v>
-      </c>
       <c r="AD2" t="n">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.81</v>
+        <v>1.9</v>
       </c>
       <c r="AI2" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="AJ2" t="n">
-        <v>2.81</v>
+        <v>2.99</v>
       </c>
       <c r="AK2" s="3" t="n">
         <v>45945.33333333334</v>
@@ -757,7 +757,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Homeboyz</t>
+          <t>Shabana</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bidco United</t>
+          <t>Posta Rangers</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,86 +798,86 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.7</v>
+        <v>1.81</v>
       </c>
       <c r="M3" t="n">
-        <v>3.05</v>
+        <v>3.04</v>
       </c>
       <c r="N3" t="n">
-        <v>5.15</v>
+        <v>4.6</v>
       </c>
       <c r="O3" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>5.52</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="S3" t="n">
         <v>2.43</v>
       </c>
-      <c r="P3" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="S3" t="n">
-        <v>2.38</v>
-      </c>
       <c r="T3" t="n">
-        <v>3.22</v>
+        <v>2.94</v>
       </c>
       <c r="U3" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="V3" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="W3" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="X3" t="n">
-        <v>2.7</v>
+        <v>2.97</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.24</v>
+        <v>2</v>
       </c>
       <c r="Z3" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG3" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AI3" t="n">
         <v>1.58</v>
       </c>
-      <c r="AA3" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG3" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>1.56</v>
-      </c>
       <c r="AJ3" t="n">
-        <v>2.99</v>
+        <v>2.81</v>
       </c>
       <c r="AK3" s="3" t="n">
-        <v>45945.375</v>
+        <v>45945.33333333334</v>
       </c>
     </row>
     <row r="4">
@@ -927,13 +927,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.53</v>
+        <v>2.54</v>
       </c>
       <c r="M4" t="n">
-        <v>2.96</v>
+        <v>3.05</v>
       </c>
       <c r="N4" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="O4" t="n">
         <v>3.22</v>
@@ -966,10 +966,10 @@
         <v>2.7</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AA4" t="n">
         <v>3.82</v>
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Leopards</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bandari</t>
+          <t>Ibri</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,83 +1056,83 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.96</v>
+        <v>1.73</v>
       </c>
       <c r="M5" t="n">
-        <v>2.83</v>
+        <v>3.5</v>
       </c>
       <c r="N5" t="n">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="O5" t="n">
-        <v>2.71</v>
+        <v>2.33</v>
       </c>
       <c r="P5" t="n">
         <v>1.94</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.52</v>
+        <v>6.26</v>
       </c>
       <c r="R5" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="S5" t="n">
-        <v>2.43</v>
+        <v>2.62</v>
       </c>
       <c r="T5" t="n">
-        <v>3.28</v>
+        <v>3.1</v>
       </c>
       <c r="U5" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="V5" t="n">
         <v>1.07</v>
       </c>
       <c r="W5" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="X5" t="n">
-        <v>2.56</v>
+        <v>2.7</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.34</v>
+        <v>2.28</v>
       </c>
       <c r="Z5" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG5" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AI5" t="n">
         <v>1.53</v>
       </c>
-      <c r="AA5" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG5" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AJ5" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="AK5" s="3" t="n">
         <v>45945.41666666666</v>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>Leopards</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ibri</t>
+          <t>Bandari</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,28 +1185,28 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.68</v>
+        <v>2.02</v>
       </c>
       <c r="M6" t="n">
-        <v>3.47</v>
+        <v>2.94</v>
       </c>
       <c r="N6" t="n">
-        <v>4.6</v>
+        <v>3.76</v>
       </c>
       <c r="O6" t="n">
-        <v>2.3</v>
+        <v>2.71</v>
       </c>
       <c r="P6" t="n">
         <v>1.94</v>
       </c>
       <c r="Q6" t="n">
-        <v>6.54</v>
+        <v>4.52</v>
       </c>
       <c r="R6" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="S6" t="n">
-        <v>2.41</v>
+        <v>2.43</v>
       </c>
       <c r="T6" t="n">
         <v>3.28</v>
@@ -1218,28 +1218,28 @@
         <v>1.07</v>
       </c>
       <c r="W6" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="X6" t="n">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.2</v>
+        <v>2.35</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AA6" t="n">
-        <v>4.25</v>
+        <v>4.4</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.17</v>
+        <v>2.01</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1252,16 +1252,16 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AH6" t="n">
-        <v>2.07</v>
+        <v>1.65</v>
       </c>
       <c r="AI6" t="n">
-        <v>1.53</v>
+        <v>1.8</v>
       </c>
       <c r="AJ6" t="n">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="AK6" s="3" t="n">
         <v>45945.41666666666</v>
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,61 +2217,61 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.24</v>
+        <v>1.99</v>
       </c>
       <c r="M14" t="n">
-        <v>2.84</v>
+        <v>3.11</v>
       </c>
       <c r="N14" t="n">
-        <v>3.12</v>
+        <v>3.39</v>
       </c>
       <c r="O14" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="P14" t="n">
-        <v>2.03</v>
+        <v>2.1</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.65</v>
+        <v>4.1</v>
       </c>
       <c r="R14" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="S14" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="T14" t="n">
-        <v>3.34</v>
+        <v>2.88</v>
       </c>
       <c r="U14" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="V14" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="W14" t="n">
-        <v>1.52</v>
+        <v>1.36</v>
       </c>
       <c r="X14" t="n">
-        <v>2.35</v>
+        <v>2.9</v>
       </c>
       <c r="Y14" t="n">
-        <v>2.5</v>
+        <v>2.12</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.53</v>
+        <v>1.72</v>
       </c>
       <c r="AA14" t="n">
-        <v>4.8</v>
+        <v>3.9</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.75</v>
+        <v>1.91</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,16 +2284,16 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AI14" t="n">
-        <v>1.83</v>
+        <v>1.72</v>
       </c>
       <c r="AJ14" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AK14" s="3" t="n">
         <v>45945.83333333334</v>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,83 +2346,83 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.99</v>
+        <v>2.24</v>
       </c>
       <c r="M15" t="n">
-        <v>3.11</v>
+        <v>2.84</v>
       </c>
       <c r="N15" t="n">
-        <v>3.39</v>
+        <v>3.12</v>
       </c>
       <c r="O15" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="P15" t="n">
-        <v>2.1</v>
+        <v>2.03</v>
       </c>
       <c r="Q15" t="n">
-        <v>4.1</v>
+        <v>3.65</v>
       </c>
       <c r="R15" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="S15" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="T15" t="n">
-        <v>2.88</v>
+        <v>3.34</v>
       </c>
       <c r="U15" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="V15" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="W15" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="X15" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG15" t="n">
         <v>1.36</v>
       </c>
-      <c r="X15" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AE15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG15" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AH15" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AI15" t="n">
-        <v>1.72</v>
+        <v>1.83</v>
       </c>
       <c r="AJ15" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="AK15" s="3" t="n">
         <v>45945.83333333334</v>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,61 +2475,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.47</v>
+        <v>2.11</v>
       </c>
       <c r="M16" t="n">
-        <v>2.93</v>
+        <v>2.87</v>
       </c>
       <c r="N16" t="n">
-        <v>2.68</v>
+        <v>3.36</v>
       </c>
       <c r="O16" t="n">
+        <v>3</v>
+      </c>
+      <c r="P16" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="T16" t="n">
         <v>3.5</v>
       </c>
-      <c r="P16" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S16" t="n">
+      <c r="U16" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="X16" t="n">
         <v>2.5</v>
       </c>
-      <c r="T16" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="W16" t="n">
+      <c r="Y16" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Z16" t="n">
         <v>1.5</v>
       </c>
-      <c r="X16" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>1.55</v>
-      </c>
       <c r="AA16" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AC16" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.74</v>
+        <v>1.65</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,16 +2542,16 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.41</v>
+        <v>1.63</v>
       </c>
       <c r="AI16" t="n">
-        <v>2.15</v>
+        <v>1.83</v>
       </c>
       <c r="AJ16" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="AK16" s="3" t="n">
         <v>45945.89583333334</v>
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,61 +2733,61 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.11</v>
+        <v>2.47</v>
       </c>
       <c r="M18" t="n">
-        <v>2.87</v>
+        <v>2.93</v>
       </c>
       <c r="N18" t="n">
-        <v>3.36</v>
+        <v>2.68</v>
       </c>
       <c r="O18" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="P18" t="n">
-        <v>1.87</v>
+        <v>1.97</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.95</v>
+        <v>3.1</v>
       </c>
       <c r="R18" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T18" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="W18" t="n">
         <v>1.5</v>
       </c>
-      <c r="S18" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="T18" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="W18" t="n">
+      <c r="X18" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Z18" t="n">
         <v>1.55</v>
       </c>
-      <c r="X18" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>1.5</v>
-      </c>
       <c r="AA18" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.65</v>
+        <v>1.74</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,16 +2800,16 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.63</v>
+        <v>1.41</v>
       </c>
       <c r="AI18" t="n">
-        <v>1.83</v>
+        <v>2.15</v>
       </c>
       <c r="AJ18" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="AK18" s="3" t="n">
         <v>45945.89583333334</v>

--- a/jogos_2025-10-15.xlsx
+++ b/jogos_2025-10-15.xlsx
@@ -643,109 +643,109 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Homeboyz</t>
+          <t>Shabana</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bidco United</t>
+          <t>Posta Rangers</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.72</v>
+        <v>1.95</v>
       </c>
       <c r="M2" t="n">
+        <v>3</v>
+      </c>
+      <c r="N2" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O2" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S2" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X2" t="n">
         <v>3.07</v>
       </c>
-      <c r="N2" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="O2" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="P2" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="S2" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="T2" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="U2" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="X2" t="n">
-        <v>2.7</v>
-      </c>
       <c r="Y2" t="n">
-        <v>2.3</v>
+        <v>1.77</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.55</v>
+        <v>1.69</v>
       </c>
       <c r="AA2" t="n">
-        <v>4.05</v>
+        <v>3.48</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.05</v>
+        <v>1.88</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.67</v>
+        <v>1.81</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['90+3']</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['45+1', '77']</t>
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="AI2" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="AJ2" t="n">
-        <v>2.99</v>
+        <v>2.81</v>
       </c>
       <c r="AK2" s="3" t="n">
         <v>45945.33333333334</v>
@@ -772,109 +772,109 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Shabana</t>
+          <t>Homeboyz</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Posta Rangers</t>
+          <t>Bidco United</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.81</v>
+        <v>1.9</v>
       </c>
       <c r="M3" t="n">
-        <v>3.04</v>
+        <v>2.9</v>
       </c>
       <c r="N3" t="n">
-        <v>4.6</v>
+        <v>3.9</v>
       </c>
       <c r="O3" t="n">
-        <v>2.53</v>
+        <v>2.9</v>
       </c>
       <c r="P3" t="n">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="Q3" t="n">
-        <v>5.52</v>
+        <v>4.7</v>
       </c>
       <c r="R3" t="n">
-        <v>1.47</v>
+        <v>1.57</v>
       </c>
       <c r="S3" t="n">
-        <v>2.43</v>
+        <v>2.26</v>
       </c>
       <c r="T3" t="n">
-        <v>2.94</v>
+        <v>3.3</v>
       </c>
       <c r="U3" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="V3" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="W3" t="n">
-        <v>1.3</v>
+        <v>1.43</v>
       </c>
       <c r="X3" t="n">
-        <v>2.97</v>
+        <v>2.52</v>
       </c>
       <c r="Y3" t="n">
-        <v>2</v>
+        <v>2.48</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.72</v>
+        <v>1.49</v>
       </c>
       <c r="AA3" t="n">
-        <v>3.48</v>
+        <v>4.55</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.87</v>
+        <v>2.04</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.82</v>
+        <v>1.68</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['34', '72', '90+5']</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['31']</t>
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.81</v>
+        <v>1.6</v>
       </c>
       <c r="AI3" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="AJ3" t="n">
-        <v>2.81</v>
+        <v>2.99</v>
       </c>
       <c r="AK3" s="3" t="n">
         <v>45945.33333333334</v>
@@ -910,91 +910,91 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.54</v>
+        <v>2.38</v>
       </c>
       <c r="M4" t="n">
         <v>3.05</v>
       </c>
       <c r="N4" t="n">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="O4" t="n">
-        <v>3.22</v>
+        <v>3.18</v>
       </c>
       <c r="P4" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.44</v>
+        <v>3.42</v>
       </c>
       <c r="R4" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="S4" t="n">
-        <v>2.46</v>
+        <v>2.49</v>
       </c>
       <c r="T4" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="U4" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="V4" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="W4" t="n">
         <v>1.36</v>
       </c>
       <c r="X4" t="n">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.82</v>
+        <v>3.92</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['86']</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['24', '42']</t>
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AH4" t="n">
         <v>1.41</v>
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>Leopards</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ibri</t>
+          <t>Bandari</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1052,65 +1052,65 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.73</v>
+        <v>2.16</v>
       </c>
       <c r="M5" t="n">
-        <v>3.5</v>
+        <v>2.75</v>
       </c>
       <c r="N5" t="n">
-        <v>4.5</v>
+        <v>3.4</v>
       </c>
       <c r="O5" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="S5" t="n">
         <v>2.33</v>
       </c>
-      <c r="P5" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>6.26</v>
-      </c>
-      <c r="R5" t="n">
+      <c r="T5" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="X5" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="Z5" t="n">
         <v>1.48</v>
       </c>
-      <c r="S5" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="T5" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="X5" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>1.56</v>
-      </c>
       <c r="AA5" t="n">
-        <v>4.5</v>
+        <v>4.75</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,16 +1123,16 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AH5" t="n">
-        <v>2.01</v>
+        <v>1.59</v>
       </c>
       <c r="AI5" t="n">
-        <v>1.53</v>
+        <v>1.8</v>
       </c>
       <c r="AJ5" t="n">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="AK5" s="3" t="n">
         <v>45945.41666666666</v>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Leopards</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bandari</t>
+          <t>Ibri</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,83 +1185,83 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.02</v>
+        <v>1.68</v>
       </c>
       <c r="M6" t="n">
-        <v>2.94</v>
+        <v>3.47</v>
       </c>
       <c r="N6" t="n">
-        <v>3.76</v>
+        <v>4.6</v>
       </c>
       <c r="O6" t="n">
-        <v>2.71</v>
+        <v>2.33</v>
       </c>
       <c r="P6" t="n">
         <v>1.94</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.52</v>
+        <v>6.26</v>
       </c>
       <c r="R6" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="S6" t="n">
-        <v>2.43</v>
+        <v>2.62</v>
       </c>
       <c r="T6" t="n">
-        <v>3.28</v>
+        <v>3.1</v>
       </c>
       <c r="U6" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="V6" t="n">
         <v>1.07</v>
       </c>
       <c r="W6" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="X6" t="n">
-        <v>2.56</v>
+        <v>2.7</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="Z6" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG6" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AI6" t="n">
         <v>1.53</v>
       </c>
-      <c r="AA6" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG6" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AJ6" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="AK6" s="3" t="n">
         <v>45945.41666666666</v>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L7" t="n">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L8" t="n">
@@ -1697,7 +1697,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L10" t="n">
@@ -1968,13 +1968,13 @@
         <v>7.2</v>
       </c>
       <c r="O12" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="P12" t="n">
         <v>2.39</v>
       </c>
       <c r="Q12" t="n">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="R12" t="n">
         <v>1.33</v>
@@ -1983,7 +1983,7 @@
         <v>3.04</v>
       </c>
       <c r="T12" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="U12" t="n">
         <v>1.44</v>
@@ -2010,10 +2010,10 @@
         <v>1.33</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2100,10 +2100,10 @@
         <v>4</v>
       </c>
       <c r="P13" t="n">
-        <v>1.96</v>
+        <v>2.11</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.64</v>
+        <v>2.54</v>
       </c>
       <c r="R13" t="n">
         <v>1.48</v>
@@ -2112,19 +2112,19 @@
         <v>2.47</v>
       </c>
       <c r="T13" t="n">
-        <v>3.38</v>
+        <v>3.22</v>
       </c>
       <c r="U13" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="V13" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="W13" t="n">
         <v>1.42</v>
       </c>
       <c r="X13" t="n">
-        <v>2.72</v>
+        <v>2.91</v>
       </c>
       <c r="Y13" t="n">
         <v>2.25</v>
@@ -2136,13 +2136,13 @@
         <v>4.2</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AC13" t="n">
         <v>1.95</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2158,7 +2158,7 @@
         <v>1.34</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AI13" t="n">
         <v>2.5</v>
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,61 +2217,61 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.99</v>
+        <v>2.24</v>
       </c>
       <c r="M14" t="n">
-        <v>3.11</v>
+        <v>2.84</v>
       </c>
       <c r="N14" t="n">
-        <v>3.39</v>
+        <v>3.12</v>
       </c>
       <c r="O14" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="P14" t="n">
-        <v>2.1</v>
+        <v>1.94</v>
       </c>
       <c r="Q14" t="n">
-        <v>4.1</v>
+        <v>3.75</v>
       </c>
       <c r="R14" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="S14" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="T14" t="n">
-        <v>2.88</v>
+        <v>3.34</v>
       </c>
       <c r="U14" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="V14" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="W14" t="n">
-        <v>1.36</v>
+        <v>1.52</v>
       </c>
       <c r="X14" t="n">
-        <v>2.9</v>
+        <v>2.35</v>
       </c>
       <c r="Y14" t="n">
-        <v>2.12</v>
+        <v>2.5</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.72</v>
+        <v>1.53</v>
       </c>
       <c r="AA14" t="n">
-        <v>3.9</v>
+        <v>4.8</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.92</v>
+        <v>1.97</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.91</v>
+        <v>1.73</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,16 +2284,16 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.67</v>
+        <v>1.58</v>
       </c>
       <c r="AI14" t="n">
-        <v>1.72</v>
+        <v>1.83</v>
       </c>
       <c r="AJ14" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="AK14" s="3" t="n">
         <v>45945.83333333334</v>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,61 +2346,61 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.24</v>
+        <v>1.99</v>
       </c>
       <c r="M15" t="n">
-        <v>2.84</v>
+        <v>3.11</v>
       </c>
       <c r="N15" t="n">
-        <v>3.12</v>
+        <v>3.39</v>
       </c>
       <c r="O15" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>3.81</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X15" t="n">
         <v>3</v>
       </c>
-      <c r="P15" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="T15" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="X15" t="n">
-        <v>2.35</v>
-      </c>
       <c r="Y15" t="n">
-        <v>2.5</v>
+        <v>2.12</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.53</v>
+        <v>1.72</v>
       </c>
       <c r="AA15" t="n">
-        <v>4.8</v>
+        <v>3.8</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.95</v>
+        <v>1.89</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.75</v>
+        <v>1.91</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,16 +2413,16 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.57</v>
+        <v>1.69</v>
       </c>
       <c r="AI15" t="n">
-        <v>1.83</v>
+        <v>1.72</v>
       </c>
       <c r="AJ15" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AK15" s="3" t="n">
         <v>45945.83333333334</v>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,61 +2475,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.11</v>
+        <v>2.47</v>
       </c>
       <c r="M16" t="n">
-        <v>2.87</v>
+        <v>2.93</v>
       </c>
       <c r="N16" t="n">
-        <v>3.36</v>
+        <v>2.68</v>
       </c>
       <c r="O16" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="P16" t="n">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.95</v>
+        <v>3.1</v>
       </c>
       <c r="R16" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T16" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="W16" t="n">
         <v>1.5</v>
       </c>
-      <c r="S16" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="T16" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="W16" t="n">
+      <c r="X16" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Z16" t="n">
         <v>1.55</v>
       </c>
-      <c r="X16" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>1.5</v>
-      </c>
       <c r="AA16" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.11</v>
+        <v>2.14</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,16 +2542,16 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.63</v>
+        <v>1.36</v>
       </c>
       <c r="AI16" t="n">
-        <v>1.83</v>
+        <v>2.15</v>
       </c>
       <c r="AJ16" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="AK16" s="3" t="n">
         <v>45945.89583333334</v>
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,61 +2604,61 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.14</v>
+        <v>2.11</v>
       </c>
       <c r="M17" t="n">
-        <v>3.14</v>
+        <v>2.87</v>
       </c>
       <c r="N17" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="O17" t="n">
         <v>2.99</v>
       </c>
-      <c r="O17" t="n">
-        <v>2.85</v>
-      </c>
       <c r="P17" t="n">
-        <v>2.17</v>
+        <v>1.86</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.06</v>
+        <v>4.3</v>
       </c>
       <c r="R17" t="n">
-        <v>1.42</v>
+        <v>1.58</v>
       </c>
       <c r="S17" t="n">
-        <v>2.65</v>
+        <v>2.29</v>
       </c>
       <c r="T17" t="n">
-        <v>2.95</v>
+        <v>3.58</v>
       </c>
       <c r="U17" t="n">
-        <v>1.35</v>
+        <v>1.23</v>
       </c>
       <c r="V17" t="n">
-        <v>1.02</v>
+        <v>1.12</v>
       </c>
       <c r="W17" t="n">
         <v>1.55</v>
       </c>
       <c r="X17" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.98</v>
+        <v>2.4</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.73</v>
+        <v>1.5</v>
       </c>
       <c r="AA17" t="n">
-        <v>4.01</v>
+        <v>4.95</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.9</v>
+        <v>2.14</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.9</v>
+        <v>1.63</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,16 +2671,16 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.3</v>
+        <v>1.39</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AI17" t="n">
         <v>1.83</v>
       </c>
       <c r="AJ17" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="AK17" s="3" t="n">
         <v>45945.89583333334</v>
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,61 +2733,61 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.47</v>
+        <v>2.14</v>
       </c>
       <c r="M18" t="n">
-        <v>2.93</v>
+        <v>3.14</v>
       </c>
       <c r="N18" t="n">
-        <v>2.68</v>
+        <v>2.99</v>
       </c>
       <c r="O18" t="n">
-        <v>3.5</v>
+        <v>2.86</v>
       </c>
       <c r="P18" t="n">
-        <v>1.97</v>
+        <v>2.17</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.1</v>
+        <v>4.08</v>
       </c>
       <c r="R18" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="S18" t="n">
-        <v>2.5</v>
+        <v>2.65</v>
       </c>
       <c r="T18" t="n">
-        <v>3.3</v>
+        <v>2.94</v>
       </c>
       <c r="U18" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="V18" t="n">
-        <v>1.1</v>
+        <v>1.02</v>
       </c>
       <c r="W18" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="X18" t="n">
         <v>2.45</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.45</v>
+        <v>1.98</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.55</v>
+        <v>1.73</v>
       </c>
       <c r="AA18" t="n">
-        <v>4.8</v>
+        <v>4.06</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="AC18" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.74</v>
+        <v>1.88</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,16 +2800,16 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.41</v>
+        <v>1.63</v>
       </c>
       <c r="AI18" t="n">
-        <v>2.15</v>
+        <v>1.83</v>
       </c>
       <c r="AJ18" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AK18" s="3" t="n">
         <v>45945.89583333334</v>
@@ -2874,49 +2874,49 @@
         <v>2.8</v>
       </c>
       <c r="P19" t="n">
-        <v>2.11</v>
+        <v>2.03</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.94</v>
+        <v>3.6</v>
       </c>
       <c r="R19" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="S19" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="T19" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="U19" t="n">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="V19" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W19" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="X19" t="n">
-        <v>2.84</v>
+        <v>3.1</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="Z19" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AC19" t="n">
         <v>1.8</v>
       </c>
-      <c r="AA19" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>1.86</v>
-      </c>
       <c r="AD19" t="n">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2929,10 +2929,10 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.58</v>
+        <v>1.67</v>
       </c>
       <c r="AI19" t="n">
         <v>1.8</v>

--- a/jogos_2025-10-15.xlsx
+++ b/jogos_2025-10-15.xlsx
@@ -643,22 +643,22 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Shabana</t>
+          <t>Homeboyz</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Posta Rangers</t>
+          <t>Bidco United</t>
         </is>
       </c>
       <c r="G2" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2" t="n">
         <v>1</v>
       </c>
-      <c r="H2" t="n">
-        <v>2</v>
-      </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J2" t="n">
         <v>1</v>
@@ -669,83 +669,83 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="M2" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="N2" t="n">
-        <v>4.5</v>
+        <v>3.9</v>
       </c>
       <c r="O2" t="n">
-        <v>2.4</v>
+        <v>2.9</v>
       </c>
       <c r="P2" t="n">
-        <v>1.97</v>
+        <v>1.8</v>
       </c>
       <c r="Q2" t="n">
-        <v>5.4</v>
+        <v>4.7</v>
       </c>
       <c r="R2" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="S2" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="T2" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="W2" t="n">
         <v>1.43</v>
       </c>
-      <c r="S2" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="T2" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="U2" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1.3</v>
-      </c>
       <c r="X2" t="n">
-        <v>3.07</v>
+        <v>2.52</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.77</v>
+        <v>2.48</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.69</v>
+        <v>1.49</v>
       </c>
       <c r="AA2" t="n">
-        <v>3.48</v>
+        <v>4.55</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.88</v>
+        <v>2.04</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.81</v>
+        <v>1.68</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>['90+3']</t>
+          <t>['34', '72', '90+5']</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>['45+1', '77']</t>
+          <t>['31']</t>
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>1.26</v>
+        <v>1.34</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.86</v>
+        <v>1.6</v>
       </c>
       <c r="AI2" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="AJ2" t="n">
-        <v>2.81</v>
+        <v>2.99</v>
       </c>
       <c r="AK2" s="3" t="n">
         <v>45945.33333333334</v>
@@ -772,22 +772,22 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Homeboyz</t>
+          <t>Shabana</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bidco United</t>
+          <t>Posta Rangers</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
         <v>1</v>
@@ -798,83 +798,83 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="M3" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="N3" t="n">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="O3" t="n">
-        <v>2.9</v>
+        <v>2.4</v>
       </c>
       <c r="P3" t="n">
-        <v>1.8</v>
+        <v>1.97</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.7</v>
+        <v>5.4</v>
       </c>
       <c r="R3" t="n">
-        <v>1.57</v>
+        <v>1.43</v>
       </c>
       <c r="S3" t="n">
-        <v>2.26</v>
+        <v>2.55</v>
       </c>
       <c r="T3" t="n">
-        <v>3.3</v>
+        <v>2.56</v>
       </c>
       <c r="U3" t="n">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="V3" t="n">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="W3" t="n">
-        <v>1.43</v>
+        <v>1.3</v>
       </c>
       <c r="X3" t="n">
-        <v>2.52</v>
+        <v>3.07</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.48</v>
+        <v>1.77</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.49</v>
+        <v>1.69</v>
       </c>
       <c r="AA3" t="n">
-        <v>4.55</v>
+        <v>3.48</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.04</v>
+        <v>1.88</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.68</v>
+        <v>1.81</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>['34', '72', '90+5']</t>
+          <t>['90+3']</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>['31']</t>
+          <t>['45+1', '77']</t>
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>1.34</v>
+        <v>1.26</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.6</v>
+        <v>1.86</v>
       </c>
       <c r="AI3" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="AJ3" t="n">
-        <v>2.99</v>
+        <v>2.81</v>
       </c>
       <c r="AK3" s="3" t="n">
         <v>45945.33333333334</v>
@@ -1959,34 +1959,34 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="M12" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="N12" t="n">
-        <v>7.2</v>
+        <v>7.5</v>
       </c>
       <c r="O12" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="P12" t="n">
-        <v>2.39</v>
+        <v>2.42</v>
       </c>
       <c r="Q12" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="R12" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="S12" t="n">
-        <v>3.04</v>
+        <v>3.3</v>
       </c>
       <c r="T12" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="U12" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="V12" t="n">
         <v>1</v>
@@ -1995,25 +1995,25 @@
         <v>1.25</v>
       </c>
       <c r="X12" t="n">
-        <v>3.54</v>
+        <v>3.78</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.78</v>
+        <v>1.86</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.92</v>
+        <v>2.09</v>
       </c>
       <c r="AA12" t="n">
-        <v>3.05</v>
+        <v>2.95</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.05</v>
+        <v>2.13</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.69</v>
+        <v>1.85</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         <v>1.19</v>
       </c>
       <c r="AH12" t="n">
-        <v>3.02</v>
+        <v>2.9</v>
       </c>
       <c r="AI12" t="n">
         <v>1.36</v>
@@ -2088,49 +2088,49 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>3.65</v>
+        <v>4.02</v>
       </c>
       <c r="M13" t="n">
-        <v>2.95</v>
+        <v>3.26</v>
       </c>
       <c r="N13" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="O13" t="n">
-        <v>4</v>
+        <v>4.84</v>
       </c>
       <c r="P13" t="n">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.54</v>
+        <v>2.58</v>
       </c>
       <c r="R13" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="S13" t="n">
-        <v>2.47</v>
+        <v>2.62</v>
       </c>
       <c r="T13" t="n">
         <v>3.22</v>
       </c>
       <c r="U13" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="V13" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="W13" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="X13" t="n">
-        <v>2.91</v>
+        <v>2.68</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AA13" t="n">
         <v>4.2</v>
@@ -2139,10 +2139,10 @@
         <v>1.17</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.34</v>
+        <v>1.39</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AI13" t="n">
         <v>2.5</v>
@@ -2217,31 +2217,31 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.24</v>
+        <v>2.42</v>
       </c>
       <c r="M14" t="n">
-        <v>2.84</v>
+        <v>3.2</v>
       </c>
       <c r="N14" t="n">
-        <v>3.12</v>
+        <v>2.95</v>
       </c>
       <c r="O14" t="n">
         <v>3</v>
       </c>
       <c r="P14" t="n">
-        <v>1.94</v>
+        <v>2.02</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.75</v>
+        <v>3.68</v>
       </c>
       <c r="R14" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="S14" t="n">
         <v>2.6</v>
       </c>
       <c r="T14" t="n">
-        <v>3.34</v>
+        <v>3.2</v>
       </c>
       <c r="U14" t="n">
         <v>1.3</v>
@@ -2250,28 +2250,28 @@
         <v>1.1</v>
       </c>
       <c r="W14" t="n">
-        <v>1.52</v>
+        <v>1.43</v>
       </c>
       <c r="X14" t="n">
-        <v>2.35</v>
+        <v>2.75</v>
       </c>
       <c r="Y14" t="n">
-        <v>2.5</v>
+        <v>2.23</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AA14" t="n">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="AB14" t="n">
         <v>1.2</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.73</v>
+        <v>1.88</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.58</v>
+        <v>1.51</v>
       </c>
       <c r="AI14" t="n">
         <v>1.83</v>
@@ -2346,46 +2346,46 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.99</v>
+        <v>2.15</v>
       </c>
       <c r="M15" t="n">
-        <v>3.11</v>
+        <v>3</v>
       </c>
       <c r="N15" t="n">
-        <v>3.39</v>
+        <v>3.5</v>
       </c>
       <c r="O15" t="n">
-        <v>2.64</v>
+        <v>2.75</v>
       </c>
       <c r="P15" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.81</v>
+        <v>3.95</v>
       </c>
       <c r="R15" t="n">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="S15" t="n">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="T15" t="n">
-        <v>2.9</v>
+        <v>3.29</v>
       </c>
       <c r="U15" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="V15" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="W15" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="X15" t="n">
-        <v>3</v>
+        <v>3.17</v>
       </c>
       <c r="Y15" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="Z15" t="n">
         <v>1.72</v>
@@ -2397,7 +2397,7 @@
         <v>1.22</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="AD15" t="n">
         <v>1.91</v>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.69</v>
+        <v>1.74</v>
       </c>
       <c r="AI15" t="n">
         <v>1.72</v>
@@ -2475,46 +2475,46 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.47</v>
+        <v>3.3</v>
       </c>
       <c r="M16" t="n">
-        <v>2.93</v>
+        <v>2.8</v>
       </c>
       <c r="N16" t="n">
-        <v>2.68</v>
+        <v>2.4</v>
       </c>
       <c r="O16" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="P16" t="n">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="R16" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="S16" t="n">
-        <v>2.5</v>
+        <v>2.34</v>
       </c>
       <c r="T16" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="U16" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="V16" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="W16" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="X16" t="n">
-        <v>2.45</v>
+        <v>2.48</v>
       </c>
       <c r="Y16" t="n">
-        <v>2.45</v>
+        <v>2.48</v>
       </c>
       <c r="Z16" t="n">
         <v>1.55</v>
@@ -2526,10 +2526,10 @@
         <v>1.13</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AI16" t="n">
         <v>2.15</v>
@@ -2604,61 +2604,61 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.11</v>
+        <v>2.15</v>
       </c>
       <c r="M17" t="n">
-        <v>2.87</v>
+        <v>3</v>
       </c>
       <c r="N17" t="n">
-        <v>3.36</v>
+        <v>3.25</v>
       </c>
       <c r="O17" t="n">
-        <v>2.99</v>
+        <v>2.95</v>
       </c>
       <c r="P17" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="R17" t="n">
         <v>1.58</v>
       </c>
       <c r="S17" t="n">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="T17" t="n">
-        <v>3.58</v>
+        <v>3.48</v>
       </c>
       <c r="U17" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="V17" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="W17" t="n">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="X17" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.4</v>
+        <v>2.53</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AA17" t="n">
-        <v>4.95</v>
+        <v>4.65</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.63</v>
+        <v>1.72</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.39</v>
+        <v>1.24</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.62</v>
+        <v>1.76</v>
       </c>
       <c r="AI17" t="n">
         <v>1.83</v>
@@ -2733,62 +2733,62 @@
         </is>
       </c>
       <c r="L18" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="M18" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N18" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="O18" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="T18" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="X18" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="Y18" t="n">
         <v>2.14</v>
       </c>
-      <c r="M18" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="N18" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="O18" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="P18" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>4.08</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="S18" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="X18" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.98</v>
-      </c>
       <c r="Z18" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AA18" t="n">
-        <v>4.06</v>
+        <v>3.54</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AC18" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AD18" t="n">
         <v>1.9</v>
       </c>
-      <c r="AD18" t="n">
-        <v>1.88</v>
-      </c>
       <c r="AE18" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AI18" t="n">
         <v>1.83</v>
@@ -2862,34 +2862,34 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.11</v>
+        <v>2.15</v>
       </c>
       <c r="M19" t="n">
-        <v>3.32</v>
+        <v>3.2</v>
       </c>
       <c r="N19" t="n">
-        <v>3.08</v>
+        <v>3.2</v>
       </c>
       <c r="O19" t="n">
         <v>2.8</v>
       </c>
       <c r="P19" t="n">
-        <v>2.03</v>
+        <v>2.21</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="R19" t="n">
         <v>1.4</v>
       </c>
       <c r="S19" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="T19" t="n">
-        <v>2.8</v>
+        <v>2.99</v>
       </c>
       <c r="U19" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="V19" t="n">
         <v>1.01</v>
@@ -2898,25 +2898,25 @@
         <v>1.33</v>
       </c>
       <c r="X19" t="n">
-        <v>3.1</v>
+        <v>3.08</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.77</v>
+        <v>1.82</v>
       </c>
       <c r="AA19" t="n">
-        <v>3.5</v>
+        <v>3.34</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.8</v>
+        <v>1.92</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2929,10 +2929,10 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.67</v>
+        <v>1.52</v>
       </c>
       <c r="AI19" t="n">
         <v>1.8</v>
